--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -2619,10 +2619,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119797531</v>
+        <v>119797559</v>
       </c>
       <c r="B19" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>752941</v>
+        <v>752988</v>
       </c>
       <c r="R19" t="n">
-        <v>7092217</v>
+        <v>7092133</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2721,10 +2721,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119799792</v>
+        <v>119797531</v>
       </c>
       <c r="B20" t="n">
-        <v>91886</v>
+        <v>89275</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,37 +2737,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>232140</v>
+        <v>6286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752934</v>
+        <v>752941</v>
       </c>
       <c r="R20" t="n">
-        <v>7092206</v>
+        <v>7092217</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,18 +2799,12 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ska återbesökas och dokumenteras ordentligt.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2943,10 +2934,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119797559</v>
+        <v>119799792</v>
       </c>
       <c r="B22" t="n">
-        <v>91884</v>
+        <v>91886</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2955,38 +2946,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>232140</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752988</v>
+        <v>752934</v>
       </c>
       <c r="R22" t="n">
-        <v>7092133</v>
+        <v>7092206</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3021,12 +3015,18 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ska återbesökas och dokumenteras ordentligt.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -2619,10 +2619,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119797559</v>
+        <v>119797531</v>
       </c>
       <c r="B19" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>752988</v>
+        <v>752941</v>
       </c>
       <c r="R19" t="n">
-        <v>7092133</v>
+        <v>7092217</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2721,10 +2721,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119797531</v>
+        <v>119799792</v>
       </c>
       <c r="B20" t="n">
-        <v>89275</v>
+        <v>91886</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,34 +2737,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6286</v>
+        <v>232140</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752941</v>
+        <v>752934</v>
       </c>
       <c r="R20" t="n">
-        <v>7092217</v>
+        <v>7092206</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,12 +2802,18 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ska återbesökas och dokumenteras ordentligt.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2823,10 +2832,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119797587</v>
+        <v>119797559</v>
       </c>
       <c r="B21" t="n">
-        <v>89212</v>
+        <v>91884</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2835,42 +2844,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1593</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752980</v>
+        <v>752988</v>
       </c>
       <c r="R21" t="n">
-        <v>7092137</v>
+        <v>7092133</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,11 +2908,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Vid stigen</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2934,10 +2934,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119799792</v>
+        <v>119797587</v>
       </c>
       <c r="B22" t="n">
-        <v>91886</v>
+        <v>89212</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2950,37 +2950,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>232140</v>
+        <v>1593</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752934</v>
+        <v>752980</v>
       </c>
       <c r="R22" t="n">
-        <v>7092206</v>
+        <v>7092137</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3017,7 +3018,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ska återbesökas och dokumenteras ordentligt.</t>
+          <t>Vid stigen</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3026,7 +3027,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -2721,10 +2721,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119799792</v>
+        <v>119797559</v>
       </c>
       <c r="B20" t="n">
-        <v>91886</v>
+        <v>91884</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2733,41 +2733,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>232140</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752934</v>
+        <v>752988</v>
       </c>
       <c r="R20" t="n">
-        <v>7092206</v>
+        <v>7092133</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,18 +2799,12 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ska återbesökas och dokumenteras ordentligt.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2832,10 +2823,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119797559</v>
+        <v>119797587</v>
       </c>
       <c r="B21" t="n">
-        <v>91884</v>
+        <v>89212</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2844,38 +2835,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>1593</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752988</v>
+        <v>752980</v>
       </c>
       <c r="R21" t="n">
-        <v>7092133</v>
+        <v>7092137</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2908,6 +2903,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Vid stigen</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2934,10 +2934,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119797587</v>
+        <v>119799792</v>
       </c>
       <c r="B22" t="n">
-        <v>89212</v>
+        <v>91886</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2950,38 +2950,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1593</v>
+        <v>232140</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752980</v>
+        <v>752934</v>
       </c>
       <c r="R22" t="n">
-        <v>7092137</v>
+        <v>7092206</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3018,7 +3017,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Vid stigen</t>
+          <t>Ska återbesökas och dokumenteras ordentligt.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,6 +3026,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -2619,10 +2619,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119797531</v>
+        <v>119797587</v>
       </c>
       <c r="B19" t="n">
-        <v>89275</v>
+        <v>89229</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2635,34 +2635,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6286</v>
+        <v>1593</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>752941</v>
+        <v>752980</v>
       </c>
       <c r="R19" t="n">
-        <v>7092217</v>
+        <v>7092137</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2695,6 +2699,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Vid stigen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,7 +2733,7 @@
         <v>119797559</v>
       </c>
       <c r="B20" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2823,10 +2832,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119797587</v>
+        <v>119799792</v>
       </c>
       <c r="B21" t="n">
-        <v>89212</v>
+        <v>91904</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,38 +2848,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1593</v>
+        <v>232140</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752980</v>
+        <v>752934</v>
       </c>
       <c r="R21" t="n">
-        <v>7092137</v>
+        <v>7092206</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2907,7 +2915,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Vid stigen</t>
+          <t>Ska återbesökas och dokumenteras ordentligt.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,6 +2924,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2934,10 +2943,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119799792</v>
+        <v>119797531</v>
       </c>
       <c r="B22" t="n">
-        <v>91886</v>
+        <v>89292</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2950,37 +2959,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>232140</v>
+        <v>6286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752934</v>
+        <v>752941</v>
       </c>
       <c r="R22" t="n">
-        <v>7092206</v>
+        <v>7092217</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,18 +3021,12 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ska återbesökas och dokumenteras ordentligt.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3048,7 +3048,7 @@
         <v>119808291</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>119934744</v>
       </c>
       <c r="B24" t="n">
-        <v>90488</v>
+        <v>90506</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3281,6 +3281,1238 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120378409</v>
+      </c>
+      <c r="B25" t="n">
+        <v>89292</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>753395</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7092342</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120375984</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>753131</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7092136</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120376488</v>
+      </c>
+      <c r="B27" t="n">
+        <v>89292</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>753131</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7092136</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120374585</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>752969</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7092237</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120374488</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>752953</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7092257</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120378569</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>753416</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7092375</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120378504</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91901</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>753400</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7092365</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120374071</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>752960</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7092251</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120374037</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>753017</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7092260</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120374050</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>752955</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7092262</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120376699</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91850</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>753325</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7092121</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2619,10 +2619,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119797587</v>
+        <v>119799792</v>
       </c>
       <c r="B19" t="n">
-        <v>89229</v>
+        <v>91904</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2635,38 +2635,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1593</v>
+        <v>232140</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>752980</v>
+        <v>752934</v>
       </c>
       <c r="R19" t="n">
-        <v>7092137</v>
+        <v>7092206</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2703,7 +2702,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Vid stigen</t>
+          <t>Ska återbesökas och dokumenteras ordentligt.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2712,6 +2711,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119797559</v>
+        <v>119797587</v>
       </c>
       <c r="B20" t="n">
-        <v>91902</v>
+        <v>89229</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2742,38 +2742,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>1593</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752988</v>
+        <v>752980</v>
       </c>
       <c r="R20" t="n">
-        <v>7092133</v>
+        <v>7092137</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,6 +2810,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Vid stigen</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2832,10 +2841,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119799792</v>
+        <v>119797531</v>
       </c>
       <c r="B21" t="n">
-        <v>91904</v>
+        <v>89292</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,37 +2857,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>232140</v>
+        <v>6286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752934</v>
+        <v>752941</v>
       </c>
       <c r="R21" t="n">
-        <v>7092206</v>
+        <v>7092217</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2913,18 +2919,12 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ska återbesökas och dokumenteras ordentligt.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119797531</v>
+        <v>119797559</v>
       </c>
       <c r="B22" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2955,25 +2955,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752941</v>
+        <v>752988</v>
       </c>
       <c r="R22" t="n">
-        <v>7092217</v>
+        <v>7092133</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120378409</v>
+        <v>120378569</v>
       </c>
       <c r="B25" t="n">
-        <v>89292</v>
+        <v>57473</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3295,25 +3295,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6286</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753395</v>
+        <v>753416</v>
       </c>
       <c r="R25" t="n">
-        <v>7092342</v>
+        <v>7092375</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3395,7 +3395,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120375984</v>
+        <v>120374585</v>
       </c>
       <c r="B26" t="n">
         <v>91902</v>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753131</v>
+        <v>752969</v>
       </c>
       <c r="R26" t="n">
-        <v>7092136</v>
+        <v>7092237</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120376488</v>
+        <v>120374488</v>
       </c>
       <c r="B27" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3519,25 +3519,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753131</v>
+        <v>752953</v>
       </c>
       <c r="R27" t="n">
-        <v>7092136</v>
+        <v>7092257</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,7 +3619,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120374585</v>
+        <v>120374037</v>
       </c>
       <c r="B28" t="n">
         <v>91902</v>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>752969</v>
+        <v>753017</v>
       </c>
       <c r="R28" t="n">
-        <v>7092237</v>
+        <v>7092260</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3731,7 +3731,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120374488</v>
+        <v>120375984</v>
       </c>
       <c r="B29" t="n">
         <v>91902</v>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752953</v>
+        <v>753131</v>
       </c>
       <c r="R29" t="n">
-        <v>7092257</v>
+        <v>7092136</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3843,10 +3843,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120378569</v>
+        <v>120376699</v>
       </c>
       <c r="B30" t="n">
-        <v>57473</v>
+        <v>91850</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3859,21 +3859,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753416</v>
+        <v>753325</v>
       </c>
       <c r="R30" t="n">
-        <v>7092375</v>
+        <v>7092121</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4179,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120374037</v>
+        <v>120376488</v>
       </c>
       <c r="B33" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4191,25 +4191,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753017</v>
+        <v>753131</v>
       </c>
       <c r="R33" t="n">
-        <v>7092260</v>
+        <v>7092136</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120376699</v>
+        <v>120378409</v>
       </c>
       <c r="B35" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4415,25 +4415,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753325</v>
+        <v>753395</v>
       </c>
       <c r="R35" t="n">
-        <v>7092121</v>
+        <v>7092342</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4512,6 +4512,3932 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120403792</v>
+      </c>
+      <c r="B36" t="n">
+        <v>90600</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>753398</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7092267</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Norrsidan lågt, gammal tall med spillkråkehack</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120403808</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>753394</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7092328</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120403801</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>753319</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7092070</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120403791</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>752978</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7092273</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120403813</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>753019</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7092243</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Mycel och fruktkroppar under hela tallågan</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120403828</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>752970</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7092257</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120403787</v>
+      </c>
+      <c r="B42" t="n">
+        <v>90506</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>752945</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7092283</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>nedfallen tallgren</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Nedfallen tallgren</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120403807</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>753398</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7092267</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>tall levande</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>Levande tall</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande tall</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120403788</v>
+      </c>
+      <c r="B44" t="n">
+        <v>90545</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>753418</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7092308</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>talllåga</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120403837</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>753040</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7092152</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120403790</v>
+      </c>
+      <c r="B46" t="n">
+        <v>89292</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>753399</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7092350</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120403803</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>752985</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7092284</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120403804</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>753034</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7092157</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120403815</v>
+      </c>
+      <c r="B49" t="n">
+        <v>84228</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>752963</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7092287</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120403814</v>
+      </c>
+      <c r="B50" t="n">
+        <v>84228</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>753350</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7092106</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120403811</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>753330</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7092111</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Under talllåga avbarkad</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120403799</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>752998</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7092239</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120403835</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>752971</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7092254</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120403812</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>753389</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7092245</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Under talllåga silverlåga</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120403794</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91844</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bankera fuligineoalba</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>753399</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7092333</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120403800</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>753420</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7092298</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120403840</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91852</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>753005</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7092225</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120403825</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>753142</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7092136</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Invid stigen</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120403826</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>753390</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7092305</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120403817</v>
+      </c>
+      <c r="B60" t="n">
+        <v>84228</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>752970</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7092203</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120403823</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91850</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>753408</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7092342</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120403834</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>753316</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7092090</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120403816</v>
+      </c>
+      <c r="B63" t="n">
+        <v>84228</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>753020</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7092255</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120403797</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91901</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>753023</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7092253</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>stigen</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120403789</v>
+      </c>
+      <c r="B65" t="n">
+        <v>89292</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>752993</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7092290</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120403821</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91850</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>753366</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7092147</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120403798</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>753328</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7092128</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120403833</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>753327</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7092129</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120403820</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91850</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>753365</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7092116</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120403836</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>753034</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7092157</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120403824</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>753398</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7092356</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -3283,10 +3283,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120378569</v>
+        <v>120378504</v>
       </c>
       <c r="B25" t="n">
-        <v>57473</v>
+        <v>91901</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3299,21 +3299,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>5448</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753416</v>
+        <v>753400</v>
       </c>
       <c r="R25" t="n">
-        <v>7092375</v>
+        <v>7092365</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3395,10 +3395,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120374585</v>
+        <v>120376699</v>
       </c>
       <c r="B26" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3411,21 +3411,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752969</v>
+        <v>753325</v>
       </c>
       <c r="R26" t="n">
-        <v>7092237</v>
+        <v>7092121</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120374488</v>
+        <v>120378569</v>
       </c>
       <c r="B27" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3523,21 +3523,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>752953</v>
+        <v>753416</v>
       </c>
       <c r="R27" t="n">
-        <v>7092257</v>
+        <v>7092375</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,10 +3619,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120374037</v>
+        <v>120376488</v>
       </c>
       <c r="B28" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753017</v>
+        <v>753131</v>
       </c>
       <c r="R28" t="n">
-        <v>7092260</v>
+        <v>7092136</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3731,10 +3731,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120375984</v>
+        <v>120374071</v>
       </c>
       <c r="B29" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3747,34 +3747,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753131</v>
+        <v>752960</v>
       </c>
       <c r="R29" t="n">
-        <v>7092136</v>
+        <v>7092251</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3843,10 +3843,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120376699</v>
+        <v>120374050</v>
       </c>
       <c r="B30" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3855,25 +3855,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753325</v>
+        <v>752955</v>
       </c>
       <c r="R30" t="n">
-        <v>7092121</v>
+        <v>7092262</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3955,10 +3955,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120378504</v>
+        <v>120374585</v>
       </c>
       <c r="B31" t="n">
-        <v>91901</v>
+        <v>91902</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3971,21 +3971,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753400</v>
+        <v>752969</v>
       </c>
       <c r="R31" t="n">
-        <v>7092365</v>
+        <v>7092237</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120374071</v>
+        <v>120375984</v>
       </c>
       <c r="B32" t="n">
-        <v>57473</v>
+        <v>91902</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4083,34 +4083,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>752960</v>
+        <v>753131</v>
       </c>
       <c r="R32" t="n">
-        <v>7092251</v>
+        <v>7092136</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4179,7 +4179,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120376488</v>
+        <v>120378409</v>
       </c>
       <c r="B33" t="n">
         <v>89292</v>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753131</v>
+        <v>753395</v>
       </c>
       <c r="R33" t="n">
-        <v>7092136</v>
+        <v>7092342</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4291,10 +4291,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120374050</v>
+        <v>120374037</v>
       </c>
       <c r="B34" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4303,25 +4303,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>752955</v>
+        <v>753017</v>
       </c>
       <c r="R34" t="n">
-        <v>7092262</v>
+        <v>7092260</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120378409</v>
+        <v>120374488</v>
       </c>
       <c r="B35" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4415,25 +4415,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753395</v>
+        <v>752953</v>
       </c>
       <c r="R35" t="n">
-        <v>7092342</v>
+        <v>7092257</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,10 +4515,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120403792</v>
+        <v>120403799</v>
       </c>
       <c r="B36" t="n">
-        <v>90600</v>
+        <v>91902</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4531,25 +4531,33 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>5449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -4558,10 +4566,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753398</v>
+        <v>752998</v>
       </c>
       <c r="R36" t="n">
-        <v>7092267</v>
+        <v>7092239</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4596,11 +4604,6 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Norrsidan lågt, gammal tall med spillkråkehack</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4610,21 +4613,6 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4641,10 +4629,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120403808</v>
+        <v>120403789</v>
       </c>
       <c r="B37" t="n">
-        <v>57336</v>
+        <v>89292</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4653,46 +4641,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753394</v>
+        <v>752993</v>
       </c>
       <c r="R37" t="n">
-        <v>7092328</v>
+        <v>7092290</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4751,10 +4731,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120403801</v>
+        <v>120403840</v>
       </c>
       <c r="B38" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4767,21 +4747,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4791,10 +4771,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753319</v>
+        <v>753005</v>
       </c>
       <c r="R38" t="n">
-        <v>7092070</v>
+        <v>7092225</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4853,10 +4833,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120403791</v>
+        <v>120403823</v>
       </c>
       <c r="B39" t="n">
-        <v>57473</v>
+        <v>91850</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4869,46 +4849,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>752978</v>
+        <v>753408</v>
       </c>
       <c r="R39" t="n">
-        <v>7092273</v>
+        <v>7092342</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4967,10 +4935,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120403813</v>
+        <v>120403836</v>
       </c>
       <c r="B40" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4979,49 +4947,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753019</v>
+        <v>753034</v>
       </c>
       <c r="R40" t="n">
-        <v>7092243</v>
+        <v>7092157</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5056,18 +5013,12 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Mycel och fruktkroppar under hela tallågan</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5086,10 +5037,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120403828</v>
+        <v>120403797</v>
       </c>
       <c r="B41" t="n">
-        <v>91881</v>
+        <v>91901</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5102,21 +5053,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5126,10 +5077,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>752970</v>
+        <v>753023</v>
       </c>
       <c r="R41" t="n">
-        <v>7092257</v>
+        <v>7092253</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5162,6 +5113,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>stigen</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5188,10 +5144,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120403787</v>
+        <v>120403812</v>
       </c>
       <c r="B42" t="n">
-        <v>90506</v>
+        <v>91862</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5200,25 +5156,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3242</v>
+        <v>4365</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5231,10 +5187,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>752945</v>
+        <v>753389</v>
       </c>
       <c r="R42" t="n">
-        <v>7092283</v>
+        <v>7092245</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5271,7 +5227,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>nedfallen tallgren</t>
+          <t>Under talllåga silverlåga</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5283,26 +5239,6 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>Nedfallen tallgren</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Nedfallen tallgren</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5319,10 +5255,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120403807</v>
+        <v>120403820</v>
       </c>
       <c r="B43" t="n">
-        <v>57336</v>
+        <v>91850</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5335,42 +5271,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753398</v>
+        <v>753365</v>
       </c>
       <c r="R43" t="n">
-        <v>7092267</v>
+        <v>7092116</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5405,11 +5333,6 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>tall levande</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5418,26 +5341,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Levande tall</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande tall</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5561,7 +5464,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120403837</v>
+        <v>120403834</v>
       </c>
       <c r="B45" t="n">
         <v>91858</v>
@@ -5601,10 +5504,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753040</v>
+        <v>753316</v>
       </c>
       <c r="R45" t="n">
-        <v>7092152</v>
+        <v>7092090</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5663,10 +5566,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120403790</v>
+        <v>120403811</v>
       </c>
       <c r="B46" t="n">
-        <v>89292</v>
+        <v>91862</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5679,21 +5582,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6286</v>
+        <v>4365</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5703,10 +5606,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753399</v>
+        <v>753330</v>
       </c>
       <c r="R46" t="n">
-        <v>7092350</v>
+        <v>7092111</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5739,6 +5642,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Under talllåga avbarkad</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5765,10 +5673,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120403803</v>
+        <v>120403814</v>
       </c>
       <c r="B47" t="n">
-        <v>91902</v>
+        <v>84228</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5777,38 +5685,49 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>3518</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>752985</v>
+        <v>753350</v>
       </c>
       <c r="R47" t="n">
-        <v>7092284</v>
+        <v>7092106</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5849,6 +5768,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5867,10 +5787,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120403804</v>
+        <v>120403790</v>
       </c>
       <c r="B48" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5879,25 +5799,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5907,10 +5827,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753034</v>
+        <v>753399</v>
       </c>
       <c r="R48" t="n">
-        <v>7092157</v>
+        <v>7092350</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5969,10 +5889,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120403815</v>
+        <v>120403791</v>
       </c>
       <c r="B49" t="n">
-        <v>84228</v>
+        <v>57473</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5981,38 +5901,50 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3518</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>752963</v>
+        <v>752978</v>
       </c>
       <c r="R49" t="n">
-        <v>7092287</v>
+        <v>7092273</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,10 +6003,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120403814</v>
+        <v>120403825</v>
       </c>
       <c r="B50" t="n">
-        <v>84228</v>
+        <v>91881</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6083,30 +6015,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3518</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6122,10 +6054,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753350</v>
+        <v>753142</v>
       </c>
       <c r="R50" t="n">
-        <v>7092106</v>
+        <v>7092136</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6158,6 +6090,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Invid stigen</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6185,10 +6122,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120403811</v>
+        <v>120403787</v>
       </c>
       <c r="B51" t="n">
-        <v>91862</v>
+        <v>90506</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6197,38 +6134,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4365</v>
+        <v>3242</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753330</v>
+        <v>752945</v>
       </c>
       <c r="R51" t="n">
-        <v>7092111</v>
+        <v>7092283</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6265,7 +6205,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Under talllåga avbarkad</t>
+          <t>nedfallen tallgren</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6274,8 +6214,29 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Nedfallen tallgren</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6292,10 +6253,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120403799</v>
+        <v>120403835</v>
       </c>
       <c r="B52" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6304,49 +6265,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>752998</v>
+        <v>752971</v>
       </c>
       <c r="R52" t="n">
-        <v>7092239</v>
+        <v>7092254</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6387,7 +6337,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6406,7 +6355,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120403835</v>
+        <v>120403833</v>
       </c>
       <c r="B53" t="n">
         <v>91858</v>
@@ -6446,10 +6395,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>752971</v>
+        <v>753327</v>
       </c>
       <c r="R53" t="n">
-        <v>7092254</v>
+        <v>7092129</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6508,10 +6457,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120403812</v>
+        <v>120403808</v>
       </c>
       <c r="B54" t="n">
-        <v>91862</v>
+        <v>57336</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6520,30 +6469,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4365</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6551,10 +6505,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753389</v>
+        <v>753394</v>
       </c>
       <c r="R54" t="n">
-        <v>7092245</v>
+        <v>7092328</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6589,18 +6543,12 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Under talllåga silverlåga</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6619,10 +6567,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120403794</v>
+        <v>120403803</v>
       </c>
       <c r="B55" t="n">
-        <v>91844</v>
+        <v>91902</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6635,41 +6583,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753399</v>
+        <v>752985</v>
       </c>
       <c r="R55" t="n">
-        <v>7092333</v>
+        <v>7092284</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6704,18 +6645,12 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6734,10 +6669,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120403800</v>
+        <v>120403807</v>
       </c>
       <c r="B56" t="n">
-        <v>91902</v>
+        <v>57336</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6750,34 +6685,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753420</v>
+        <v>753398</v>
       </c>
       <c r="R56" t="n">
-        <v>7092298</v>
+        <v>7092267</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6812,6 +6755,11 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>tall levande</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6820,6 +6768,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Levande tall</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande tall</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6836,10 +6804,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120403840</v>
+        <v>120403816</v>
       </c>
       <c r="B57" t="n">
-        <v>91852</v>
+        <v>84228</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6848,38 +6816,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>3518</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753005</v>
+        <v>753020</v>
       </c>
       <c r="R57" t="n">
-        <v>7092225</v>
+        <v>7092255</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6920,6 +6899,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6938,10 +6918,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120403825</v>
+        <v>120403792</v>
       </c>
       <c r="B58" t="n">
-        <v>91881</v>
+        <v>90600</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6954,33 +6934,25 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -6989,10 +6961,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753142</v>
+        <v>753398</v>
       </c>
       <c r="R58" t="n">
-        <v>7092136</v>
+        <v>7092267</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7029,7 +7001,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Invid stigen</t>
+          <t>Norrsidan lågt, gammal tall med spillkråkehack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7041,6 +7013,21 @@
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7057,10 +7044,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120403826</v>
+        <v>120403794</v>
       </c>
       <c r="B59" t="n">
-        <v>91881</v>
+        <v>91844</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7073,21 +7060,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5966</v>
+        <v>3100</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -7095,11 +7082,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
@@ -7108,10 +7091,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753390</v>
+        <v>753399</v>
       </c>
       <c r="R59" t="n">
-        <v>7092305</v>
+        <v>7092333</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7144,6 +7127,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7285,10 +7273,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120403823</v>
+        <v>120403828</v>
       </c>
       <c r="B61" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7301,21 +7289,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7325,10 +7313,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753408</v>
+        <v>752970</v>
       </c>
       <c r="R61" t="n">
-        <v>7092342</v>
+        <v>7092257</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7387,10 +7375,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120403834</v>
+        <v>120403824</v>
       </c>
       <c r="B62" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7399,38 +7387,49 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753316</v>
+        <v>753398</v>
       </c>
       <c r="R62" t="n">
-        <v>7092090</v>
+        <v>7092356</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7471,6 +7470,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7489,10 +7489,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120403816</v>
+        <v>120403798</v>
       </c>
       <c r="B63" t="n">
-        <v>84228</v>
+        <v>91902</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7501,49 +7501,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3518</v>
+        <v>5449</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753020</v>
+        <v>753328</v>
       </c>
       <c r="R63" t="n">
-        <v>7092255</v>
+        <v>7092128</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7578,13 +7567,17 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7603,10 +7596,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120403797</v>
+        <v>120403800</v>
       </c>
       <c r="B64" t="n">
-        <v>91901</v>
+        <v>91902</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7619,21 +7612,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7643,10 +7636,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753023</v>
+        <v>753420</v>
       </c>
       <c r="R64" t="n">
-        <v>7092253</v>
+        <v>7092298</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7679,11 +7672,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>stigen</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7710,10 +7698,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120403789</v>
+        <v>120403821</v>
       </c>
       <c r="B65" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7722,25 +7710,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7750,10 +7738,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>752993</v>
+        <v>753366</v>
       </c>
       <c r="R65" t="n">
-        <v>7092290</v>
+        <v>7092147</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7812,10 +7800,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120403821</v>
+        <v>120403815</v>
       </c>
       <c r="B66" t="n">
-        <v>91850</v>
+        <v>84228</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7824,25 +7812,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4361</v>
+        <v>3518</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7852,10 +7840,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753366</v>
+        <v>752963</v>
       </c>
       <c r="R66" t="n">
-        <v>7092147</v>
+        <v>7092287</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7914,10 +7902,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120403798</v>
+        <v>120403813</v>
       </c>
       <c r="B67" t="n">
-        <v>91902</v>
+        <v>91862</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7926,38 +7914,49 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753328</v>
+        <v>753019</v>
       </c>
       <c r="R67" t="n">
-        <v>7092128</v>
+        <v>7092243</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7994,7 +7993,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>Mycel och fruktkroppar under hela tallågan</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8003,6 +8002,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8021,10 +8021,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120403833</v>
+        <v>120403801</v>
       </c>
       <c r="B68" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8033,25 +8033,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753327</v>
+        <v>753319</v>
       </c>
       <c r="R68" t="n">
-        <v>7092129</v>
+        <v>7092070</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8123,10 +8123,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120403820</v>
+        <v>120403826</v>
       </c>
       <c r="B69" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8139,34 +8139,45 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753365</v>
+        <v>753390</v>
       </c>
       <c r="R69" t="n">
-        <v>7092116</v>
+        <v>7092305</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8207,6 +8218,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8225,10 +8237,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120403836</v>
+        <v>120403804</v>
       </c>
       <c r="B70" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8237,25 +8249,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8327,10 +8339,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120403824</v>
+        <v>120403837</v>
       </c>
       <c r="B71" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8339,49 +8351,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753398</v>
+        <v>753040</v>
       </c>
       <c r="R71" t="n">
-        <v>7092356</v>
+        <v>7092152</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8422,7 +8423,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -4067,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120375984</v>
+        <v>120378409</v>
       </c>
       <c r="B32" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4079,25 +4079,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753131</v>
+        <v>753395</v>
       </c>
       <c r="R32" t="n">
-        <v>7092136</v>
+        <v>7092342</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4179,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120378409</v>
+        <v>120375984</v>
       </c>
       <c r="B33" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4191,25 +4191,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753395</v>
+        <v>753131</v>
       </c>
       <c r="R33" t="n">
-        <v>7092342</v>
+        <v>7092136</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -3395,10 +3395,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120376699</v>
+        <v>120374585</v>
       </c>
       <c r="B26" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3411,21 +3411,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753325</v>
+        <v>752969</v>
       </c>
       <c r="R26" t="n">
-        <v>7092121</v>
+        <v>7092237</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120378569</v>
+        <v>120378409</v>
       </c>
       <c r="B27" t="n">
-        <v>57473</v>
+        <v>89292</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3519,25 +3519,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753416</v>
+        <v>753395</v>
       </c>
       <c r="R27" t="n">
-        <v>7092375</v>
+        <v>7092342</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,10 +3619,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120376488</v>
+        <v>120374488</v>
       </c>
       <c r="B28" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753131</v>
+        <v>752953</v>
       </c>
       <c r="R28" t="n">
-        <v>7092136</v>
+        <v>7092257</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3843,10 +3843,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120374050</v>
+        <v>120376699</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3855,25 +3855,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>752955</v>
+        <v>753325</v>
       </c>
       <c r="R30" t="n">
-        <v>7092262</v>
+        <v>7092121</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3955,10 +3955,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120374585</v>
+        <v>120376488</v>
       </c>
       <c r="B31" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3967,25 +3967,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>752969</v>
+        <v>753131</v>
       </c>
       <c r="R31" t="n">
-        <v>7092237</v>
+        <v>7092136</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120378409</v>
+        <v>120375984</v>
       </c>
       <c r="B32" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4079,25 +4079,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753395</v>
+        <v>753131</v>
       </c>
       <c r="R32" t="n">
-        <v>7092342</v>
+        <v>7092136</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4179,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120375984</v>
+        <v>120374050</v>
       </c>
       <c r="B33" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4191,25 +4191,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753131</v>
+        <v>752955</v>
       </c>
       <c r="R33" t="n">
-        <v>7092136</v>
+        <v>7092262</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120374488</v>
+        <v>120378569</v>
       </c>
       <c r="B35" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4419,21 +4419,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>752953</v>
+        <v>753416</v>
       </c>
       <c r="R35" t="n">
-        <v>7092257</v>
+        <v>7092375</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,10 +4515,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120403799</v>
+        <v>120403817</v>
       </c>
       <c r="B36" t="n">
-        <v>91902</v>
+        <v>84228</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4527,30 +4527,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5449</v>
+        <v>3518</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4566,10 +4566,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>752998</v>
+        <v>752970</v>
       </c>
       <c r="R36" t="n">
-        <v>7092239</v>
+        <v>7092203</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4629,10 +4629,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120403789</v>
+        <v>120403823</v>
       </c>
       <c r="B37" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4641,25 +4641,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>752993</v>
+        <v>753408</v>
       </c>
       <c r="R37" t="n">
-        <v>7092290</v>
+        <v>7092342</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4731,10 +4731,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120403840</v>
+        <v>120403790</v>
       </c>
       <c r="B38" t="n">
-        <v>91852</v>
+        <v>89292</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4743,25 +4743,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753005</v>
+        <v>753399</v>
       </c>
       <c r="R38" t="n">
-        <v>7092225</v>
+        <v>7092350</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4833,10 +4833,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120403823</v>
+        <v>120403792</v>
       </c>
       <c r="B39" t="n">
-        <v>91850</v>
+        <v>90600</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4849,34 +4849,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753408</v>
+        <v>753398</v>
       </c>
       <c r="R39" t="n">
-        <v>7092342</v>
+        <v>7092267</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4911,14 +4914,35 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Norrsidan lågt, gammal tall med spillkråkehack</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4935,10 +4959,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120403836</v>
+        <v>120403825</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4947,38 +4971,49 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753034</v>
+        <v>753142</v>
       </c>
       <c r="R40" t="n">
-        <v>7092157</v>
+        <v>7092136</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5013,12 +5048,18 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Invid stigen</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5037,10 +5078,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120403797</v>
+        <v>120403814</v>
       </c>
       <c r="B41" t="n">
-        <v>91901</v>
+        <v>84228</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5049,38 +5090,49 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5448</v>
+        <v>3518</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753023</v>
+        <v>753350</v>
       </c>
       <c r="R41" t="n">
-        <v>7092253</v>
+        <v>7092106</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5115,17 +5167,13 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>stigen</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5255,10 +5303,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120403820</v>
+        <v>120403787</v>
       </c>
       <c r="B43" t="n">
-        <v>91850</v>
+        <v>90506</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5271,34 +5319,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>3242</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753365</v>
+        <v>752945</v>
       </c>
       <c r="R43" t="n">
-        <v>7092116</v>
+        <v>7092283</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5333,14 +5384,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>nedfallen tallgren</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Nedfallen tallgren</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5357,10 +5434,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120403788</v>
+        <v>120403834</v>
       </c>
       <c r="B44" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5373,21 +5450,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5397,10 +5474,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753418</v>
+        <v>753316</v>
       </c>
       <c r="R44" t="n">
-        <v>7092308</v>
+        <v>7092090</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5433,11 +5510,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>talllåga</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5464,7 +5536,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120403834</v>
+        <v>120403837</v>
       </c>
       <c r="B45" t="n">
         <v>91858</v>
@@ -5504,10 +5576,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753316</v>
+        <v>753040</v>
       </c>
       <c r="R45" t="n">
-        <v>7092090</v>
+        <v>7092152</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5566,10 +5638,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120403811</v>
+        <v>120403836</v>
       </c>
       <c r="B46" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5578,25 +5650,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5606,10 +5678,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753330</v>
+        <v>753034</v>
       </c>
       <c r="R46" t="n">
-        <v>7092111</v>
+        <v>7092157</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5642,11 +5714,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Under talllåga avbarkad</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5673,10 +5740,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120403814</v>
+        <v>120403803</v>
       </c>
       <c r="B47" t="n">
-        <v>84228</v>
+        <v>91902</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5685,49 +5752,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3518</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753350</v>
+        <v>752985</v>
       </c>
       <c r="R47" t="n">
-        <v>7092106</v>
+        <v>7092284</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5768,7 +5824,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5787,7 +5842,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120403790</v>
+        <v>120403789</v>
       </c>
       <c r="B48" t="n">
         <v>89292</v>
@@ -5827,10 +5882,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753399</v>
+        <v>752993</v>
       </c>
       <c r="R48" t="n">
-        <v>7092350</v>
+        <v>7092290</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5889,10 +5944,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120403791</v>
+        <v>120403833</v>
       </c>
       <c r="B49" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5901,50 +5956,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>752978</v>
+        <v>753327</v>
       </c>
       <c r="R49" t="n">
-        <v>7092273</v>
+        <v>7092129</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6003,10 +6046,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120403825</v>
+        <v>120403821</v>
       </c>
       <c r="B50" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6019,45 +6062,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753142</v>
+        <v>753366</v>
       </c>
       <c r="R50" t="n">
-        <v>7092136</v>
+        <v>7092147</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6092,18 +6124,12 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Invid stigen</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6122,10 +6148,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120403787</v>
+        <v>120403800</v>
       </c>
       <c r="B51" t="n">
-        <v>90506</v>
+        <v>91902</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6138,37 +6164,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3242</v>
+        <v>5449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>752945</v>
+        <v>753420</v>
       </c>
       <c r="R51" t="n">
-        <v>7092283</v>
+        <v>7092298</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6203,40 +6226,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>nedfallen tallgren</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>Nedfallen tallgren</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Nedfallen tallgren</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6253,10 +6250,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120403835</v>
+        <v>120403801</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6265,25 +6262,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6293,10 +6290,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>752971</v>
+        <v>753319</v>
       </c>
       <c r="R52" t="n">
-        <v>7092254</v>
+        <v>7092070</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6355,10 +6352,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120403833</v>
+        <v>120403808</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6367,38 +6364,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753327</v>
+        <v>753394</v>
       </c>
       <c r="R53" t="n">
-        <v>7092129</v>
+        <v>7092328</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6457,7 +6462,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120403808</v>
+        <v>120403807</v>
       </c>
       <c r="B54" t="n">
         <v>57336</v>
@@ -6505,10 +6510,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753394</v>
+        <v>753398</v>
       </c>
       <c r="R54" t="n">
-        <v>7092328</v>
+        <v>7092267</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6543,6 +6548,11 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>tall levande</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6551,6 +6561,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Levande tall</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande tall</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6567,10 +6597,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120403803</v>
+        <v>120403824</v>
       </c>
       <c r="B55" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6583,34 +6613,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>752985</v>
+        <v>753398</v>
       </c>
       <c r="R55" t="n">
-        <v>7092284</v>
+        <v>7092356</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6651,6 +6692,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6669,10 +6711,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120403807</v>
+        <v>120403799</v>
       </c>
       <c r="B56" t="n">
-        <v>57336</v>
+        <v>91902</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6685,31 +6727,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6717,10 +6762,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753398</v>
+        <v>752998</v>
       </c>
       <c r="R56" t="n">
-        <v>7092267</v>
+        <v>7092239</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6755,39 +6800,15 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>tall levande</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL56" t="inlineStr">
-        <is>
-          <t>Levande tall</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande tall</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6804,10 +6825,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120403816</v>
+        <v>120403804</v>
       </c>
       <c r="B57" t="n">
-        <v>84228</v>
+        <v>91902</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6816,49 +6837,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3518</v>
+        <v>5449</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753020</v>
+        <v>753034</v>
       </c>
       <c r="R57" t="n">
-        <v>7092255</v>
+        <v>7092157</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6899,7 +6909,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6918,10 +6927,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120403792</v>
+        <v>120403791</v>
       </c>
       <c r="B58" t="n">
-        <v>90600</v>
+        <v>57473</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6934,26 +6943,35 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6961,10 +6979,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753398</v>
+        <v>752978</v>
       </c>
       <c r="R58" t="n">
-        <v>7092267</v>
+        <v>7092273</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6999,35 +7017,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Norrsidan lågt, gammal tall med spillkråkehack</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7044,10 +7041,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120403794</v>
+        <v>120403813</v>
       </c>
       <c r="B59" t="n">
-        <v>91844</v>
+        <v>91862</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7056,33 +7053,37 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3100</v>
+        <v>4365</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
@@ -7091,10 +7092,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753399</v>
+        <v>753019</v>
       </c>
       <c r="R59" t="n">
-        <v>7092333</v>
+        <v>7092243</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7131,7 +7132,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
+          <t>Mycel och fruktkroppar under hela tallågan</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7159,10 +7160,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120403817</v>
+        <v>120403794</v>
       </c>
       <c r="B60" t="n">
-        <v>84228</v>
+        <v>91844</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7171,37 +7172,33 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3518</v>
+        <v>3100</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
@@ -7210,10 +7207,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>752970</v>
+        <v>753399</v>
       </c>
       <c r="R60" t="n">
-        <v>7092203</v>
+        <v>7092333</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7246,6 +7243,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7273,10 +7275,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120403828</v>
+        <v>120403815</v>
       </c>
       <c r="B61" t="n">
-        <v>91881</v>
+        <v>84228</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7285,25 +7287,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>3518</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7313,10 +7315,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>752970</v>
+        <v>752963</v>
       </c>
       <c r="R61" t="n">
-        <v>7092257</v>
+        <v>7092287</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7375,10 +7377,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120403824</v>
+        <v>120403788</v>
       </c>
       <c r="B62" t="n">
-        <v>91881</v>
+        <v>90545</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7387,49 +7389,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753398</v>
+        <v>753418</v>
       </c>
       <c r="R62" t="n">
-        <v>7092356</v>
+        <v>7092308</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7464,13 +7455,17 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>talllåga</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7489,10 +7484,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120403798</v>
+        <v>120403840</v>
       </c>
       <c r="B63" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7505,21 +7500,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7529,10 +7524,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753328</v>
+        <v>753005</v>
       </c>
       <c r="R63" t="n">
-        <v>7092128</v>
+        <v>7092225</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7565,11 +7560,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7596,10 +7586,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120403800</v>
+        <v>120403820</v>
       </c>
       <c r="B64" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7612,21 +7602,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7636,10 +7626,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753420</v>
+        <v>753365</v>
       </c>
       <c r="R64" t="n">
-        <v>7092298</v>
+        <v>7092116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7698,10 +7688,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120403821</v>
+        <v>120403828</v>
       </c>
       <c r="B65" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7714,21 +7704,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7738,10 +7728,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753366</v>
+        <v>752970</v>
       </c>
       <c r="R65" t="n">
-        <v>7092147</v>
+        <v>7092257</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7800,10 +7790,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120403815</v>
+        <v>120403826</v>
       </c>
       <c r="B66" t="n">
-        <v>84228</v>
+        <v>91881</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7812,38 +7802,49 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3518</v>
+        <v>5966</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>752963</v>
+        <v>753390</v>
       </c>
       <c r="R66" t="n">
-        <v>7092287</v>
+        <v>7092305</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7884,6 +7885,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7902,10 +7904,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120403813</v>
+        <v>120403816</v>
       </c>
       <c r="B67" t="n">
-        <v>91862</v>
+        <v>84228</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7914,30 +7916,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4365</v>
+        <v>3518</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7953,10 +7955,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753019</v>
+        <v>753020</v>
       </c>
       <c r="R67" t="n">
-        <v>7092243</v>
+        <v>7092255</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7989,11 +7991,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Mycel och fruktkroppar under hela tallågan</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8021,7 +8018,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120403801</v>
+        <v>120403798</v>
       </c>
       <c r="B68" t="n">
         <v>91902</v>
@@ -8061,10 +8058,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753319</v>
+        <v>753328</v>
       </c>
       <c r="R68" t="n">
-        <v>7092070</v>
+        <v>7092128</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8097,6 +8094,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8123,10 +8125,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120403826</v>
+        <v>120403797</v>
       </c>
       <c r="B69" t="n">
-        <v>91881</v>
+        <v>91901</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8139,45 +8141,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753390</v>
+        <v>753023</v>
       </c>
       <c r="R69" t="n">
-        <v>7092305</v>
+        <v>7092253</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8212,13 +8203,17 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>stigen</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8237,10 +8232,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120403804</v>
+        <v>120403811</v>
       </c>
       <c r="B70" t="n">
-        <v>91902</v>
+        <v>91862</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8249,25 +8244,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8277,10 +8272,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753034</v>
+        <v>753330</v>
       </c>
       <c r="R70" t="n">
-        <v>7092157</v>
+        <v>7092111</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8313,6 +8308,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Under talllåga avbarkad</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8339,7 +8339,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120403837</v>
+        <v>120403835</v>
       </c>
       <c r="B71" t="n">
         <v>91858</v>
@@ -8379,10 +8379,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753040</v>
+        <v>752971</v>
       </c>
       <c r="R71" t="n">
-        <v>7092152</v>
+        <v>7092254</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -3283,10 +3283,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120378504</v>
+        <v>120376699</v>
       </c>
       <c r="B25" t="n">
-        <v>91901</v>
+        <v>91850</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3299,21 +3299,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753400</v>
+        <v>753325</v>
       </c>
       <c r="R25" t="n">
-        <v>7092365</v>
+        <v>7092121</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3395,7 +3395,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120374585</v>
+        <v>120374488</v>
       </c>
       <c r="B26" t="n">
         <v>91902</v>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752969</v>
+        <v>752953</v>
       </c>
       <c r="R26" t="n">
-        <v>7092237</v>
+        <v>7092257</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,7 +3507,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120378409</v>
+        <v>120376488</v>
       </c>
       <c r="B27" t="n">
         <v>89292</v>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753395</v>
+        <v>753131</v>
       </c>
       <c r="R27" t="n">
-        <v>7092342</v>
+        <v>7092136</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,10 +3619,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120374488</v>
+        <v>120378504</v>
       </c>
       <c r="B28" t="n">
-        <v>91902</v>
+        <v>91901</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3635,21 +3635,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>752953</v>
+        <v>753400</v>
       </c>
       <c r="R28" t="n">
-        <v>7092257</v>
+        <v>7092365</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3731,10 +3731,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120374071</v>
+        <v>120374585</v>
       </c>
       <c r="B29" t="n">
-        <v>57473</v>
+        <v>91902</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3747,34 +3747,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752960</v>
+        <v>752969</v>
       </c>
       <c r="R29" t="n">
-        <v>7092251</v>
+        <v>7092237</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3843,10 +3843,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120376699</v>
+        <v>120374050</v>
       </c>
       <c r="B30" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3855,25 +3855,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753325</v>
+        <v>752955</v>
       </c>
       <c r="R30" t="n">
-        <v>7092121</v>
+        <v>7092262</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3955,10 +3955,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120376488</v>
+        <v>120374037</v>
       </c>
       <c r="B31" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3967,25 +3967,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753131</v>
+        <v>753017</v>
       </c>
       <c r="R31" t="n">
-        <v>7092136</v>
+        <v>7092260</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120375984</v>
+        <v>120374071</v>
       </c>
       <c r="B32" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4083,34 +4083,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753131</v>
+        <v>752960</v>
       </c>
       <c r="R32" t="n">
-        <v>7092136</v>
+        <v>7092251</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4179,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120374050</v>
+        <v>120375984</v>
       </c>
       <c r="B33" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4191,25 +4191,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>752955</v>
+        <v>753131</v>
       </c>
       <c r="R33" t="n">
-        <v>7092262</v>
+        <v>7092136</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4291,10 +4291,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120374037</v>
+        <v>120378569</v>
       </c>
       <c r="B34" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753017</v>
+        <v>753416</v>
       </c>
       <c r="R34" t="n">
-        <v>7092260</v>
+        <v>7092375</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120378569</v>
+        <v>120378409</v>
       </c>
       <c r="B35" t="n">
-        <v>57473</v>
+        <v>89292</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4415,25 +4415,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753416</v>
+        <v>753395</v>
       </c>
       <c r="R35" t="n">
-        <v>7092375</v>
+        <v>7092342</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,10 +4515,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120403817</v>
+        <v>120403823</v>
       </c>
       <c r="B36" t="n">
-        <v>84228</v>
+        <v>91850</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4527,49 +4527,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3518</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>752970</v>
+        <v>753408</v>
       </c>
       <c r="R36" t="n">
-        <v>7092203</v>
+        <v>7092342</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4610,7 +4599,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4629,10 +4617,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120403823</v>
+        <v>120403813</v>
       </c>
       <c r="B37" t="n">
-        <v>91850</v>
+        <v>91862</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4641,38 +4629,49 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753408</v>
+        <v>753019</v>
       </c>
       <c r="R37" t="n">
-        <v>7092342</v>
+        <v>7092243</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4707,12 +4706,18 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Mycel och fruktkroppar under hela tallågan</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4731,10 +4736,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120403790</v>
+        <v>120403799</v>
       </c>
       <c r="B38" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4743,38 +4748,49 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753399</v>
+        <v>752998</v>
       </c>
       <c r="R38" t="n">
-        <v>7092350</v>
+        <v>7092239</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4815,6 +4831,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4959,10 +4976,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120403825</v>
+        <v>120403833</v>
       </c>
       <c r="B40" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4971,49 +4988,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753142</v>
+        <v>753327</v>
       </c>
       <c r="R40" t="n">
-        <v>7092136</v>
+        <v>7092129</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5048,18 +5054,12 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Invid stigen</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120403814</v>
+        <v>120403789</v>
       </c>
       <c r="B41" t="n">
-        <v>84228</v>
+        <v>89292</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5090,49 +5090,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3518</v>
+        <v>6286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753350</v>
+        <v>752993</v>
       </c>
       <c r="R41" t="n">
-        <v>7092106</v>
+        <v>7092290</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5173,7 +5162,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5192,10 +5180,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120403812</v>
+        <v>120403817</v>
       </c>
       <c r="B42" t="n">
-        <v>91862</v>
+        <v>84228</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5204,29 +5192,37 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4365</v>
+        <v>3518</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -5235,10 +5231,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753389</v>
+        <v>752970</v>
       </c>
       <c r="R42" t="n">
-        <v>7092245</v>
+        <v>7092203</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5271,11 +5267,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Under talllåga silverlåga</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5303,10 +5294,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120403787</v>
+        <v>120403808</v>
       </c>
       <c r="B43" t="n">
-        <v>90506</v>
+        <v>57336</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5319,26 +5310,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3242</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5346,10 +5342,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>752945</v>
+        <v>753394</v>
       </c>
       <c r="R43" t="n">
-        <v>7092283</v>
+        <v>7092328</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5384,40 +5380,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>nedfallen tallgren</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Nedfallen tallgren</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Nedfallen tallgren</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5434,10 +5404,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120403834</v>
+        <v>120403826</v>
       </c>
       <c r="B44" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5446,38 +5416,49 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753316</v>
+        <v>753390</v>
       </c>
       <c r="R44" t="n">
-        <v>7092090</v>
+        <v>7092305</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5518,6 +5499,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5536,7 +5518,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120403837</v>
+        <v>120403836</v>
       </c>
       <c r="B45" t="n">
         <v>91858</v>
@@ -5576,10 +5558,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753040</v>
+        <v>753034</v>
       </c>
       <c r="R45" t="n">
-        <v>7092152</v>
+        <v>7092157</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5638,10 +5620,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120403836</v>
+        <v>120403788</v>
       </c>
       <c r="B46" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5654,21 +5636,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5678,10 +5660,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753034</v>
+        <v>753418</v>
       </c>
       <c r="R46" t="n">
-        <v>7092157</v>
+        <v>7092308</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5714,6 +5696,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>talllåga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5740,10 +5727,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120403803</v>
+        <v>120403791</v>
       </c>
       <c r="B47" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5756,34 +5743,46 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>752985</v>
+        <v>752978</v>
       </c>
       <c r="R47" t="n">
-        <v>7092284</v>
+        <v>7092273</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5842,10 +5841,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120403789</v>
+        <v>120403834</v>
       </c>
       <c r="B48" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5854,25 +5853,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5882,10 +5881,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>752993</v>
+        <v>753316</v>
       </c>
       <c r="R48" t="n">
-        <v>7092290</v>
+        <v>7092090</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5944,10 +5943,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120403833</v>
+        <v>120403800</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5956,25 +5955,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5984,10 +5983,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753327</v>
+        <v>753420</v>
       </c>
       <c r="R49" t="n">
-        <v>7092129</v>
+        <v>7092298</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6046,10 +6045,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120403821</v>
+        <v>120403803</v>
       </c>
       <c r="B50" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6062,21 +6061,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6086,10 +6085,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753366</v>
+        <v>752985</v>
       </c>
       <c r="R50" t="n">
-        <v>7092147</v>
+        <v>7092284</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6148,7 +6147,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120403800</v>
+        <v>120403798</v>
       </c>
       <c r="B51" t="n">
         <v>91902</v>
@@ -6188,10 +6187,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753420</v>
+        <v>753328</v>
       </c>
       <c r="R51" t="n">
-        <v>7092298</v>
+        <v>7092128</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6224,6 +6223,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6250,7 +6254,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120403801</v>
+        <v>120403804</v>
       </c>
       <c r="B52" t="n">
         <v>91902</v>
@@ -6290,10 +6294,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753319</v>
+        <v>753034</v>
       </c>
       <c r="R52" t="n">
-        <v>7092070</v>
+        <v>7092157</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6352,10 +6356,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120403808</v>
+        <v>120403790</v>
       </c>
       <c r="B53" t="n">
-        <v>57336</v>
+        <v>89292</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6364,46 +6368,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753394</v>
+        <v>753399</v>
       </c>
       <c r="R53" t="n">
-        <v>7092328</v>
+        <v>7092350</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6462,10 +6458,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120403807</v>
+        <v>120403816</v>
       </c>
       <c r="B54" t="n">
-        <v>57336</v>
+        <v>84228</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6474,35 +6470,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>3518</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6510,10 +6509,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753398</v>
+        <v>753020</v>
       </c>
       <c r="R54" t="n">
-        <v>7092267</v>
+        <v>7092255</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6548,39 +6547,15 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>tall levande</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL54" t="inlineStr">
-        <is>
-          <t>Levande tall</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande tall</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6597,10 +6572,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120403824</v>
+        <v>120403787</v>
       </c>
       <c r="B55" t="n">
-        <v>91881</v>
+        <v>90506</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6613,33 +6588,25 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>3242</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -6648,10 +6615,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753398</v>
+        <v>752945</v>
       </c>
       <c r="R55" t="n">
-        <v>7092356</v>
+        <v>7092283</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6686,6 +6653,11 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>nedfallen tallgren</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6695,6 +6667,26 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Nedfallen tallgren</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6711,7 +6703,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120403799</v>
+        <v>120403801</v>
       </c>
       <c r="B56" t="n">
         <v>91902</v>
@@ -6744,28 +6736,17 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>752998</v>
+        <v>753319</v>
       </c>
       <c r="R56" t="n">
-        <v>7092239</v>
+        <v>7092070</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6806,7 +6787,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6825,10 +6805,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120403804</v>
+        <v>120403824</v>
       </c>
       <c r="B57" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6841,34 +6821,45 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753034</v>
+        <v>753398</v>
       </c>
       <c r="R57" t="n">
-        <v>7092157</v>
+        <v>7092356</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6909,6 +6900,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6927,10 +6919,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120403791</v>
+        <v>120403797</v>
       </c>
       <c r="B58" t="n">
-        <v>57473</v>
+        <v>91901</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6943,46 +6935,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>5448</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>752978</v>
+        <v>753023</v>
       </c>
       <c r="R58" t="n">
-        <v>7092273</v>
+        <v>7092253</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7015,6 +6995,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>stigen</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7041,7 +7026,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120403813</v>
+        <v>120403812</v>
       </c>
       <c r="B59" t="n">
         <v>91862</v>
@@ -7074,16 +7059,8 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
@@ -7092,10 +7069,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753019</v>
+        <v>753389</v>
       </c>
       <c r="R59" t="n">
-        <v>7092243</v>
+        <v>7092245</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7132,7 +7109,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Mycel och fruktkroppar under hela tallågan</t>
+          <t>Under talllåga silverlåga</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7160,10 +7137,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120403794</v>
+        <v>120403807</v>
       </c>
       <c r="B60" t="n">
-        <v>91844</v>
+        <v>57336</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7176,30 +7153,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3100</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7207,10 +7185,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753399</v>
+        <v>753398</v>
       </c>
       <c r="R60" t="n">
-        <v>7092333</v>
+        <v>7092267</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7247,7 +7225,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
+          <t>tall levande</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7256,9 +7234,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Levande tall</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande tall</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7275,10 +7272,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120403815</v>
+        <v>120403794</v>
       </c>
       <c r="B61" t="n">
-        <v>84228</v>
+        <v>91844</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7287,38 +7284,45 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3518</v>
+        <v>3100</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>752963</v>
+        <v>753399</v>
       </c>
       <c r="R61" t="n">
-        <v>7092287</v>
+        <v>7092333</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7353,12 +7357,18 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7377,10 +7387,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120403788</v>
+        <v>120403840</v>
       </c>
       <c r="B62" t="n">
-        <v>90545</v>
+        <v>91852</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7389,25 +7399,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>4362</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7417,10 +7427,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753418</v>
+        <v>753005</v>
       </c>
       <c r="R62" t="n">
-        <v>7092308</v>
+        <v>7092225</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7453,11 +7463,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>talllåga</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7484,10 +7489,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120403840</v>
+        <v>120403828</v>
       </c>
       <c r="B63" t="n">
-        <v>91852</v>
+        <v>91881</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7500,21 +7505,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7524,10 +7529,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753005</v>
+        <v>752970</v>
       </c>
       <c r="R63" t="n">
-        <v>7092225</v>
+        <v>7092257</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7586,10 +7591,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120403820</v>
+        <v>120403825</v>
       </c>
       <c r="B64" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7602,34 +7607,45 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753365</v>
+        <v>753142</v>
       </c>
       <c r="R64" t="n">
-        <v>7092116</v>
+        <v>7092136</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7664,12 +7680,18 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Invid stigen</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7688,10 +7710,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120403828</v>
+        <v>120403835</v>
       </c>
       <c r="B65" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7700,25 +7722,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7728,10 +7750,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>752970</v>
+        <v>752971</v>
       </c>
       <c r="R65" t="n">
-        <v>7092257</v>
+        <v>7092254</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7790,10 +7812,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120403826</v>
+        <v>120403820</v>
       </c>
       <c r="B66" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7806,45 +7828,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753390</v>
+        <v>753365</v>
       </c>
       <c r="R66" t="n">
-        <v>7092305</v>
+        <v>7092116</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7885,7 +7896,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7904,10 +7914,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120403816</v>
+        <v>120403811</v>
       </c>
       <c r="B67" t="n">
-        <v>84228</v>
+        <v>91862</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7916,49 +7926,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3518</v>
+        <v>4365</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753020</v>
+        <v>753330</v>
       </c>
       <c r="R67" t="n">
-        <v>7092255</v>
+        <v>7092111</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7993,13 +7992,17 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Under talllåga avbarkad</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8018,10 +8021,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120403798</v>
+        <v>120403821</v>
       </c>
       <c r="B68" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8034,21 +8037,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8058,10 +8061,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753328</v>
+        <v>753366</v>
       </c>
       <c r="R68" t="n">
-        <v>7092128</v>
+        <v>7092147</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8094,11 +8097,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8125,10 +8123,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120403797</v>
+        <v>120403815</v>
       </c>
       <c r="B69" t="n">
-        <v>91901</v>
+        <v>84228</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8137,25 +8135,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5448</v>
+        <v>3518</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8165,10 +8163,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753023</v>
+        <v>752963</v>
       </c>
       <c r="R69" t="n">
-        <v>7092253</v>
+        <v>7092287</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8201,11 +8199,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>stigen</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8232,10 +8225,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120403811</v>
+        <v>120403814</v>
       </c>
       <c r="B70" t="n">
-        <v>91862</v>
+        <v>84228</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8244,38 +8237,49 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4365</v>
+        <v>3518</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753330</v>
+        <v>753350</v>
       </c>
       <c r="R70" t="n">
-        <v>7092111</v>
+        <v>7092106</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8310,17 +8314,13 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Under talllåga avbarkad</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8339,7 +8339,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120403835</v>
+        <v>120403837</v>
       </c>
       <c r="B71" t="n">
         <v>91858</v>
@@ -8379,10 +8379,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>752971</v>
+        <v>753040</v>
       </c>
       <c r="R71" t="n">
-        <v>7092254</v>
+        <v>7092152</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -5620,10 +5620,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120403788</v>
+        <v>120403791</v>
       </c>
       <c r="B46" t="n">
-        <v>90545</v>
+        <v>57473</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5632,38 +5632,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753418</v>
+        <v>752978</v>
       </c>
       <c r="R46" t="n">
-        <v>7092308</v>
+        <v>7092273</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5696,11 +5708,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>talllåga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5727,10 +5734,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120403791</v>
+        <v>120403788</v>
       </c>
       <c r="B47" t="n">
-        <v>57473</v>
+        <v>90545</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5739,50 +5746,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>752978</v>
+        <v>753418</v>
       </c>
       <c r="R47" t="n">
-        <v>7092273</v>
+        <v>7092308</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5815,6 +5810,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>talllåga</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6356,10 +6356,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120403790</v>
+        <v>120403787</v>
       </c>
       <c r="B53" t="n">
-        <v>89292</v>
+        <v>90506</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6368,38 +6368,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6286</v>
+        <v>3242</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753399</v>
+        <v>752945</v>
       </c>
       <c r="R53" t="n">
-        <v>7092350</v>
+        <v>7092283</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6434,14 +6437,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>nedfallen tallgren</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Nedfallen tallgren</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6572,10 +6601,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120403787</v>
+        <v>120403790</v>
       </c>
       <c r="B55" t="n">
-        <v>90506</v>
+        <v>89292</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6584,41 +6613,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3242</v>
+        <v>6286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>752945</v>
+        <v>753399</v>
       </c>
       <c r="R55" t="n">
-        <v>7092283</v>
+        <v>7092350</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6653,40 +6679,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>nedfallen tallgren</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL55" t="inlineStr">
-        <is>
-          <t>Nedfallen tallgren</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Nedfallen tallgren</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7489,10 +7489,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120403828</v>
+        <v>120403835</v>
       </c>
       <c r="B63" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7501,25 +7501,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>752970</v>
+        <v>752971</v>
       </c>
       <c r="R63" t="n">
-        <v>7092257</v>
+        <v>7092254</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7591,10 +7591,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120403825</v>
+        <v>120403820</v>
       </c>
       <c r="B64" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7607,45 +7607,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753142</v>
+        <v>753365</v>
       </c>
       <c r="R64" t="n">
-        <v>7092136</v>
+        <v>7092116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7680,18 +7669,12 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Invid stigen</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7710,10 +7693,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120403835</v>
+        <v>120403828</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7722,25 +7705,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7750,10 +7733,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>752971</v>
+        <v>752970</v>
       </c>
       <c r="R65" t="n">
-        <v>7092254</v>
+        <v>7092257</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7812,10 +7795,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120403820</v>
+        <v>120403825</v>
       </c>
       <c r="B66" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7828,34 +7811,45 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753365</v>
+        <v>753142</v>
       </c>
       <c r="R66" t="n">
-        <v>7092116</v>
+        <v>7092136</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7890,12 +7884,18 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Invid stigen</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -3283,10 +3283,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120376699</v>
+        <v>120375984</v>
       </c>
       <c r="B25" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3299,21 +3299,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753325</v>
+        <v>753131</v>
       </c>
       <c r="R25" t="n">
-        <v>7092121</v>
+        <v>7092136</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3395,10 +3395,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120374488</v>
+        <v>120374050</v>
       </c>
       <c r="B26" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3407,25 +3407,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752953</v>
+        <v>752955</v>
       </c>
       <c r="R26" t="n">
-        <v>7092257</v>
+        <v>7092262</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120376488</v>
+        <v>120376699</v>
       </c>
       <c r="B27" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3519,25 +3519,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753131</v>
+        <v>753325</v>
       </c>
       <c r="R27" t="n">
-        <v>7092136</v>
+        <v>7092121</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,10 +3619,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120378504</v>
+        <v>120374585</v>
       </c>
       <c r="B28" t="n">
-        <v>91901</v>
+        <v>91902</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3635,21 +3635,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753400</v>
+        <v>752969</v>
       </c>
       <c r="R28" t="n">
-        <v>7092365</v>
+        <v>7092237</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3731,7 +3731,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120374585</v>
+        <v>120374488</v>
       </c>
       <c r="B29" t="n">
         <v>91902</v>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752969</v>
+        <v>752953</v>
       </c>
       <c r="R29" t="n">
-        <v>7092237</v>
+        <v>7092257</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3843,10 +3843,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120374050</v>
+        <v>120374071</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3855,38 +3855,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>752955</v>
+        <v>752960</v>
       </c>
       <c r="R30" t="n">
-        <v>7092262</v>
+        <v>7092251</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3955,10 +3955,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120374037</v>
+        <v>120376488</v>
       </c>
       <c r="B31" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3967,25 +3967,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753017</v>
+        <v>753131</v>
       </c>
       <c r="R31" t="n">
-        <v>7092260</v>
+        <v>7092136</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120374071</v>
+        <v>120374037</v>
       </c>
       <c r="B32" t="n">
-        <v>57473</v>
+        <v>91902</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4083,34 +4083,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>752960</v>
+        <v>753017</v>
       </c>
       <c r="R32" t="n">
-        <v>7092251</v>
+        <v>7092260</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4179,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120375984</v>
+        <v>120378504</v>
       </c>
       <c r="B33" t="n">
-        <v>91902</v>
+        <v>91901</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4195,21 +4195,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753131</v>
+        <v>753400</v>
       </c>
       <c r="R33" t="n">
-        <v>7092136</v>
+        <v>7092365</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4515,10 +4515,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120403823</v>
+        <v>120403824</v>
       </c>
       <c r="B36" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4531,34 +4531,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753408</v>
+        <v>753398</v>
       </c>
       <c r="R36" t="n">
-        <v>7092342</v>
+        <v>7092356</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4599,6 +4610,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4617,10 +4629,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120403813</v>
+        <v>120403826</v>
       </c>
       <c r="B37" t="n">
-        <v>91862</v>
+        <v>91881</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4629,30 +4641,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4365</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4668,10 +4680,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753019</v>
+        <v>753390</v>
       </c>
       <c r="R37" t="n">
-        <v>7092243</v>
+        <v>7092305</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4704,11 +4716,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Mycel och fruktkroppar under hela tallågan</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4736,10 +4743,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120403799</v>
+        <v>120403835</v>
       </c>
       <c r="B38" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4748,49 +4755,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>752998</v>
+        <v>752971</v>
       </c>
       <c r="R38" t="n">
-        <v>7092239</v>
+        <v>7092254</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4831,7 +4827,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4850,10 +4845,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120403792</v>
+        <v>120403808</v>
       </c>
       <c r="B39" t="n">
-        <v>90600</v>
+        <v>57336</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4866,26 +4861,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753398</v>
+        <v>753394</v>
       </c>
       <c r="R39" t="n">
-        <v>7092267</v>
+        <v>7092328</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4931,35 +4931,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Norrsidan lågt, gammal tall med spillkråkehack</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4976,7 +4955,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120403833</v>
+        <v>120403837</v>
       </c>
       <c r="B40" t="n">
         <v>91858</v>
@@ -5016,10 +4995,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753327</v>
+        <v>753040</v>
       </c>
       <c r="R40" t="n">
-        <v>7092129</v>
+        <v>7092152</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5078,10 +5057,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120403789</v>
+        <v>120403820</v>
       </c>
       <c r="B41" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5090,25 +5069,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5118,10 +5097,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>752993</v>
+        <v>753365</v>
       </c>
       <c r="R41" t="n">
-        <v>7092290</v>
+        <v>7092116</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5180,10 +5159,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120403817</v>
+        <v>120403788</v>
       </c>
       <c r="B42" t="n">
-        <v>84228</v>
+        <v>90545</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5196,45 +5175,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3518</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>752970</v>
+        <v>753418</v>
       </c>
       <c r="R42" t="n">
-        <v>7092203</v>
+        <v>7092308</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5269,13 +5237,17 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>talllåga</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5294,10 +5266,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120403808</v>
+        <v>120403798</v>
       </c>
       <c r="B43" t="n">
-        <v>57336</v>
+        <v>91902</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5310,42 +5282,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753394</v>
+        <v>753328</v>
       </c>
       <c r="R43" t="n">
-        <v>7092328</v>
+        <v>7092128</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5378,6 +5342,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5404,10 +5373,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120403826</v>
+        <v>120403799</v>
       </c>
       <c r="B44" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5420,26 +5389,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5455,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753390</v>
+        <v>752998</v>
       </c>
       <c r="R44" t="n">
-        <v>7092305</v>
+        <v>7092239</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5518,10 +5487,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120403836</v>
+        <v>120403823</v>
       </c>
       <c r="B45" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5530,25 +5499,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5558,10 +5527,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753034</v>
+        <v>753408</v>
       </c>
       <c r="R45" t="n">
-        <v>7092157</v>
+        <v>7092342</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5620,10 +5589,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120403791</v>
+        <v>120403807</v>
       </c>
       <c r="B46" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5636,33 +5605,29 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5672,10 +5637,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>752978</v>
+        <v>753398</v>
       </c>
       <c r="R46" t="n">
-        <v>7092273</v>
+        <v>7092267</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5710,6 +5675,11 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>tall levande</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5718,6 +5688,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>Levande tall</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande tall</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5734,10 +5724,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120403788</v>
+        <v>120403811</v>
       </c>
       <c r="B47" t="n">
-        <v>90545</v>
+        <v>91862</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5746,25 +5736,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>4365</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5774,10 +5764,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753418</v>
+        <v>753330</v>
       </c>
       <c r="R47" t="n">
-        <v>7092308</v>
+        <v>7092111</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5814,7 +5804,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>talllåga</t>
+          <t>Under talllåga avbarkad</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5841,10 +5831,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120403834</v>
+        <v>120403803</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5853,25 +5843,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5881,10 +5871,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753316</v>
+        <v>752985</v>
       </c>
       <c r="R48" t="n">
-        <v>7092090</v>
+        <v>7092284</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5943,10 +5933,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120403800</v>
+        <v>120403828</v>
       </c>
       <c r="B49" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5959,21 +5949,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5983,10 +5973,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753420</v>
+        <v>752970</v>
       </c>
       <c r="R49" t="n">
-        <v>7092298</v>
+        <v>7092257</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6045,10 +6035,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120403803</v>
+        <v>120403815</v>
       </c>
       <c r="B50" t="n">
-        <v>91902</v>
+        <v>84228</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6057,25 +6047,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5449</v>
+        <v>3518</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6085,10 +6075,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>752985</v>
+        <v>752963</v>
       </c>
       <c r="R50" t="n">
-        <v>7092284</v>
+        <v>7092287</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6147,10 +6137,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120403798</v>
+        <v>120403816</v>
       </c>
       <c r="B51" t="n">
-        <v>91902</v>
+        <v>84228</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6159,38 +6149,49 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5449</v>
+        <v>3518</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753328</v>
+        <v>753020</v>
       </c>
       <c r="R51" t="n">
-        <v>7092128</v>
+        <v>7092255</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6225,17 +6226,13 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6254,10 +6251,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120403804</v>
+        <v>120403840</v>
       </c>
       <c r="B52" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6270,21 +6267,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6294,10 +6291,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753034</v>
+        <v>753005</v>
       </c>
       <c r="R52" t="n">
-        <v>7092157</v>
+        <v>7092225</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6356,10 +6353,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120403787</v>
+        <v>120403825</v>
       </c>
       <c r="B53" t="n">
-        <v>90506</v>
+        <v>91881</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6372,25 +6369,33 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3242</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -6399,10 +6404,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>752945</v>
+        <v>753142</v>
       </c>
       <c r="R53" t="n">
-        <v>7092283</v>
+        <v>7092136</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6439,7 +6444,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>nedfallen tallgren</t>
+          <t>Invid stigen</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6451,26 +6456,6 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>Nedfallen tallgren</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Nedfallen tallgren</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6487,10 +6472,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120403816</v>
+        <v>120403833</v>
       </c>
       <c r="B54" t="n">
-        <v>84228</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6503,45 +6488,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3518</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753020</v>
+        <v>753327</v>
       </c>
       <c r="R54" t="n">
-        <v>7092255</v>
+        <v>7092129</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6582,7 +6556,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6601,10 +6574,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120403790</v>
+        <v>120403812</v>
       </c>
       <c r="B55" t="n">
-        <v>89292</v>
+        <v>91862</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6617,34 +6590,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6286</v>
+        <v>4365</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753399</v>
+        <v>753389</v>
       </c>
       <c r="R55" t="n">
-        <v>7092350</v>
+        <v>7092245</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6679,12 +6655,18 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Under talllåga silverlåga</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6703,10 +6685,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120403801</v>
+        <v>120403787</v>
       </c>
       <c r="B56" t="n">
-        <v>91902</v>
+        <v>90506</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6719,34 +6701,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5449</v>
+        <v>3242</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753319</v>
+        <v>752945</v>
       </c>
       <c r="R56" t="n">
-        <v>7092070</v>
+        <v>7092283</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6781,14 +6766,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>nedfallen tallgren</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Nedfallen tallgren</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6805,10 +6816,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120403824</v>
+        <v>120403801</v>
       </c>
       <c r="B57" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6821,45 +6832,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753398</v>
+        <v>753319</v>
       </c>
       <c r="R57" t="n">
-        <v>7092356</v>
+        <v>7092070</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6900,7 +6900,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6919,10 +6918,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120403797</v>
+        <v>120403792</v>
       </c>
       <c r="B58" t="n">
-        <v>91901</v>
+        <v>90600</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6935,34 +6934,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753023</v>
+        <v>753398</v>
       </c>
       <c r="R58" t="n">
-        <v>7092253</v>
+        <v>7092267</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6999,7 +7001,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>stigen</t>
+          <t>Norrsidan lågt, gammal tall med spillkråkehack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7008,8 +7010,24 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7026,10 +7044,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120403812</v>
+        <v>120403814</v>
       </c>
       <c r="B59" t="n">
-        <v>91862</v>
+        <v>84228</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7038,29 +7056,37 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4365</v>
+        <v>3518</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
@@ -7069,10 +7095,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753389</v>
+        <v>753350</v>
       </c>
       <c r="R59" t="n">
-        <v>7092245</v>
+        <v>7092106</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7105,11 +7131,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Under talllåga silverlåga</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7137,10 +7158,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120403807</v>
+        <v>120403821</v>
       </c>
       <c r="B60" t="n">
-        <v>57336</v>
+        <v>91850</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7153,42 +7174,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753398</v>
+        <v>753366</v>
       </c>
       <c r="R60" t="n">
-        <v>7092267</v>
+        <v>7092147</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7223,11 +7236,6 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>tall levande</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7236,26 +7244,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL60" t="inlineStr">
-        <is>
-          <t>Levande tall</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande tall</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7272,10 +7260,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120403794</v>
+        <v>120403804</v>
       </c>
       <c r="B61" t="n">
-        <v>91844</v>
+        <v>91902</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7288,41 +7276,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753399</v>
+        <v>753034</v>
       </c>
       <c r="R61" t="n">
-        <v>7092333</v>
+        <v>7092157</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7357,18 +7338,12 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7387,10 +7362,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120403840</v>
+        <v>120403790</v>
       </c>
       <c r="B62" t="n">
-        <v>91852</v>
+        <v>89292</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7399,25 +7374,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7427,10 +7402,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753005</v>
+        <v>753399</v>
       </c>
       <c r="R62" t="n">
-        <v>7092225</v>
+        <v>7092350</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7489,7 +7464,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120403835</v>
+        <v>120403834</v>
       </c>
       <c r="B63" t="n">
         <v>91858</v>
@@ -7529,10 +7504,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>752971</v>
+        <v>753316</v>
       </c>
       <c r="R63" t="n">
-        <v>7092254</v>
+        <v>7092090</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7591,10 +7566,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120403820</v>
+        <v>120403817</v>
       </c>
       <c r="B64" t="n">
-        <v>91850</v>
+        <v>84228</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7603,38 +7578,49 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4361</v>
+        <v>3518</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753365</v>
+        <v>752970</v>
       </c>
       <c r="R64" t="n">
-        <v>7092116</v>
+        <v>7092203</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7675,6 +7661,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7693,10 +7680,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120403828</v>
+        <v>120403797</v>
       </c>
       <c r="B65" t="n">
-        <v>91881</v>
+        <v>91901</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7709,21 +7696,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7733,10 +7720,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>752970</v>
+        <v>753023</v>
       </c>
       <c r="R65" t="n">
-        <v>7092257</v>
+        <v>7092253</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7769,6 +7756,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>stigen</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7795,10 +7787,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120403825</v>
+        <v>120403789</v>
       </c>
       <c r="B66" t="n">
-        <v>91881</v>
+        <v>89292</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7807,49 +7799,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5966</v>
+        <v>6286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753142</v>
+        <v>752993</v>
       </c>
       <c r="R66" t="n">
-        <v>7092136</v>
+        <v>7092290</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7884,18 +7865,12 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Invid stigen</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7914,10 +7889,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120403811</v>
+        <v>120403800</v>
       </c>
       <c r="B67" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7926,25 +7901,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7954,10 +7929,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753330</v>
+        <v>753420</v>
       </c>
       <c r="R67" t="n">
-        <v>7092111</v>
+        <v>7092298</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7990,11 +7965,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Under talllåga avbarkad</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8021,10 +7991,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120403821</v>
+        <v>120403813</v>
       </c>
       <c r="B68" t="n">
-        <v>91850</v>
+        <v>91862</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8033,38 +8003,49 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753366</v>
+        <v>753019</v>
       </c>
       <c r="R68" t="n">
-        <v>7092147</v>
+        <v>7092243</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8099,12 +8080,18 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Mycel och fruktkroppar under hela tallågan</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8123,10 +8110,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120403815</v>
+        <v>120403836</v>
       </c>
       <c r="B69" t="n">
-        <v>84228</v>
+        <v>91858</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8139,21 +8126,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3518</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8163,10 +8150,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>752963</v>
+        <v>753034</v>
       </c>
       <c r="R69" t="n">
-        <v>7092287</v>
+        <v>7092157</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8225,10 +8212,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120403814</v>
+        <v>120403791</v>
       </c>
       <c r="B70" t="n">
-        <v>84228</v>
+        <v>57473</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8237,38 +8224,39 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3518</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8276,10 +8264,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>753350</v>
+        <v>752978</v>
       </c>
       <c r="R70" t="n">
-        <v>7092106</v>
+        <v>7092273</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8320,7 +8308,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8339,10 +8326,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120403837</v>
+        <v>120403794</v>
       </c>
       <c r="B71" t="n">
-        <v>91858</v>
+        <v>91844</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8351,38 +8338,45 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753040</v>
+        <v>753399</v>
       </c>
       <c r="R71" t="n">
-        <v>7092152</v>
+        <v>7092333</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8417,12 +8411,18 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -3395,10 +3395,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120374050</v>
+        <v>120374037</v>
       </c>
       <c r="B26" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3407,25 +3407,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>752955</v>
+        <v>753017</v>
       </c>
       <c r="R26" t="n">
-        <v>7092262</v>
+        <v>7092260</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120376699</v>
+        <v>120378504</v>
       </c>
       <c r="B27" t="n">
-        <v>91850</v>
+        <v>91901</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3523,21 +3523,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753325</v>
+        <v>753400</v>
       </c>
       <c r="R27" t="n">
-        <v>7092121</v>
+        <v>7092365</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,7 +3619,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120374585</v>
+        <v>120374488</v>
       </c>
       <c r="B28" t="n">
         <v>91902</v>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>752969</v>
+        <v>752953</v>
       </c>
       <c r="R28" t="n">
-        <v>7092237</v>
+        <v>7092257</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3731,10 +3731,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120374488</v>
+        <v>120378409</v>
       </c>
       <c r="B29" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3743,25 +3743,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752953</v>
+        <v>753395</v>
       </c>
       <c r="R29" t="n">
-        <v>7092257</v>
+        <v>7092342</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3843,10 +3843,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120374071</v>
+        <v>120376699</v>
       </c>
       <c r="B30" t="n">
-        <v>57473</v>
+        <v>91850</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3859,34 +3859,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>752960</v>
+        <v>753325</v>
       </c>
       <c r="R30" t="n">
-        <v>7092251</v>
+        <v>7092121</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3955,10 +3955,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120376488</v>
+        <v>120374585</v>
       </c>
       <c r="B31" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3967,25 +3967,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753131</v>
+        <v>752969</v>
       </c>
       <c r="R31" t="n">
-        <v>7092136</v>
+        <v>7092237</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120374037</v>
+        <v>120374071</v>
       </c>
       <c r="B32" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4083,34 +4083,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753017</v>
+        <v>752960</v>
       </c>
       <c r="R32" t="n">
-        <v>7092260</v>
+        <v>7092251</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4179,10 +4179,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120378504</v>
+        <v>120376488</v>
       </c>
       <c r="B33" t="n">
-        <v>91901</v>
+        <v>89292</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4191,25 +4191,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5448</v>
+        <v>6286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753400</v>
+        <v>753131</v>
       </c>
       <c r="R33" t="n">
-        <v>7092365</v>
+        <v>7092136</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4291,10 +4291,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120378569</v>
+        <v>120374050</v>
       </c>
       <c r="B34" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4303,25 +4303,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753416</v>
+        <v>752955</v>
       </c>
       <c r="R34" t="n">
-        <v>7092375</v>
+        <v>7092262</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4403,10 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120378409</v>
+        <v>120378569</v>
       </c>
       <c r="B35" t="n">
-        <v>89292</v>
+        <v>57473</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4415,25 +4415,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6286</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753395</v>
+        <v>753416</v>
       </c>
       <c r="R35" t="n">
-        <v>7092342</v>
+        <v>7092375</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4629,7 +4629,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120403826</v>
+        <v>120403828</v>
       </c>
       <c r="B37" t="n">
         <v>91881</v>
@@ -4662,28 +4662,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753390</v>
+        <v>752970</v>
       </c>
       <c r="R37" t="n">
-        <v>7092305</v>
+        <v>7092257</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4724,7 +4713,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4743,10 +4731,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120403835</v>
+        <v>120403817</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>84228</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4759,34 +4747,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>3518</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>752971</v>
+        <v>752970</v>
       </c>
       <c r="R38" t="n">
-        <v>7092254</v>
+        <v>7092203</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4827,6 +4826,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120403808</v>
+        <v>120403825</v>
       </c>
       <c r="B39" t="n">
-        <v>57336</v>
+        <v>91881</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4861,31 +4861,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4893,10 +4896,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753394</v>
+        <v>753142</v>
       </c>
       <c r="R39" t="n">
-        <v>7092328</v>
+        <v>7092136</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4931,12 +4934,18 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Invid stigen</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4955,10 +4964,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120403837</v>
+        <v>120403798</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4967,25 +4976,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4995,10 +5004,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753040</v>
+        <v>753328</v>
       </c>
       <c r="R40" t="n">
-        <v>7092152</v>
+        <v>7092128</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5031,6 +5040,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5057,10 +5071,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120403820</v>
+        <v>120403788</v>
       </c>
       <c r="B41" t="n">
-        <v>91850</v>
+        <v>90545</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5069,25 +5083,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5097,10 +5111,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753365</v>
+        <v>753418</v>
       </c>
       <c r="R41" t="n">
-        <v>7092116</v>
+        <v>7092308</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5133,6 +5147,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>talllåga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5159,10 +5178,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120403788</v>
+        <v>120403800</v>
       </c>
       <c r="B42" t="n">
-        <v>90545</v>
+        <v>91902</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5171,25 +5190,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>5449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5199,10 +5218,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753418</v>
+        <v>753420</v>
       </c>
       <c r="R42" t="n">
-        <v>7092308</v>
+        <v>7092298</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5235,11 +5254,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>talllåga</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5266,7 +5280,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120403798</v>
+        <v>120403801</v>
       </c>
       <c r="B43" t="n">
         <v>91902</v>
@@ -5306,10 +5320,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753328</v>
+        <v>753319</v>
       </c>
       <c r="R43" t="n">
-        <v>7092128</v>
+        <v>7092070</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5342,11 +5356,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5373,10 +5382,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120403799</v>
+        <v>120403791</v>
       </c>
       <c r="B44" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5389,34 +5398,35 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5424,10 +5434,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>752998</v>
+        <v>752978</v>
       </c>
       <c r="R44" t="n">
-        <v>7092239</v>
+        <v>7092273</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5468,7 +5478,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5487,10 +5496,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120403823</v>
+        <v>120403803</v>
       </c>
       <c r="B45" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5503,21 +5512,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5527,10 +5536,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753408</v>
+        <v>752985</v>
       </c>
       <c r="R45" t="n">
-        <v>7092342</v>
+        <v>7092284</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5589,10 +5598,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120403807</v>
+        <v>120403797</v>
       </c>
       <c r="B46" t="n">
-        <v>57336</v>
+        <v>91901</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5605,42 +5614,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>5448</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753398</v>
+        <v>753023</v>
       </c>
       <c r="R46" t="n">
-        <v>7092267</v>
+        <v>7092253</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5677,7 +5678,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>tall levande</t>
+          <t>stigen</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5688,26 +5689,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Levande tall</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande tall</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5724,10 +5705,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120403811</v>
+        <v>120403823</v>
       </c>
       <c r="B47" t="n">
-        <v>91862</v>
+        <v>91850</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5736,25 +5717,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5764,10 +5745,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753330</v>
+        <v>753408</v>
       </c>
       <c r="R47" t="n">
-        <v>7092111</v>
+        <v>7092342</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5800,11 +5781,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Under talllåga avbarkad</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5831,10 +5807,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120403803</v>
+        <v>120403833</v>
       </c>
       <c r="B48" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5843,25 +5819,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5871,10 +5847,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>752985</v>
+        <v>753327</v>
       </c>
       <c r="R48" t="n">
-        <v>7092284</v>
+        <v>7092129</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5933,10 +5909,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120403828</v>
+        <v>120403836</v>
       </c>
       <c r="B49" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5945,25 +5921,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5973,10 +5949,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>752970</v>
+        <v>753034</v>
       </c>
       <c r="R49" t="n">
-        <v>7092257</v>
+        <v>7092157</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6137,10 +6113,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120403816</v>
+        <v>120403813</v>
       </c>
       <c r="B51" t="n">
-        <v>84228</v>
+        <v>91862</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6149,30 +6125,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3518</v>
+        <v>4365</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6188,10 +6164,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753020</v>
+        <v>753019</v>
       </c>
       <c r="R51" t="n">
-        <v>7092255</v>
+        <v>7092243</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6224,6 +6200,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Mycel och fruktkroppar under hela tallågan</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6353,10 +6334,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120403825</v>
+        <v>120403792</v>
       </c>
       <c r="B53" t="n">
-        <v>91881</v>
+        <v>90600</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6369,33 +6350,25 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -6404,10 +6377,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753142</v>
+        <v>753398</v>
       </c>
       <c r="R53" t="n">
-        <v>7092136</v>
+        <v>7092267</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6444,7 +6417,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Invid stigen</t>
+          <t>Norrsidan lågt, gammal tall med spillkråkehack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6456,6 +6429,21 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6472,10 +6460,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120403833</v>
+        <v>120403789</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6484,25 +6472,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6512,10 +6500,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753327</v>
+        <v>752993</v>
       </c>
       <c r="R54" t="n">
-        <v>7092129</v>
+        <v>7092290</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6574,7 +6562,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120403812</v>
+        <v>120403811</v>
       </c>
       <c r="B55" t="n">
         <v>91862</v>
@@ -6608,19 +6596,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753389</v>
+        <v>753330</v>
       </c>
       <c r="R55" t="n">
-        <v>7092245</v>
+        <v>7092111</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6657,7 +6642,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Under talllåga silverlåga</t>
+          <t>Under talllåga avbarkad</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6666,7 +6651,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6685,10 +6669,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120403787</v>
+        <v>120403794</v>
       </c>
       <c r="B56" t="n">
-        <v>90506</v>
+        <v>91844</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6701,24 +6685,28 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3242</v>
+        <v>3100</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -6728,10 +6716,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>752945</v>
+        <v>753399</v>
       </c>
       <c r="R56" t="n">
-        <v>7092283</v>
+        <v>7092333</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6768,7 +6756,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>nedfallen tallgren</t>
+          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6780,26 +6768,6 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL56" t="inlineStr">
-        <is>
-          <t>Nedfallen tallgren</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Nedfallen tallgren</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6816,10 +6784,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120403801</v>
+        <v>120403787</v>
       </c>
       <c r="B57" t="n">
-        <v>91902</v>
+        <v>90506</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6832,34 +6800,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5449</v>
+        <v>3242</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753319</v>
+        <v>752945</v>
       </c>
       <c r="R57" t="n">
-        <v>7092070</v>
+        <v>7092283</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6894,14 +6865,40 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>nedfallen tallgren</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Nedfallen tallgren</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -6918,10 +6915,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120403792</v>
+        <v>120403835</v>
       </c>
       <c r="B58" t="n">
-        <v>90600</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6930,41 +6927,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753398</v>
+        <v>752971</v>
       </c>
       <c r="R58" t="n">
-        <v>7092267</v>
+        <v>7092254</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6999,35 +6993,14 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Norrsidan lågt, gammal tall med spillkråkehack</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7044,10 +7017,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120403814</v>
+        <v>120403826</v>
       </c>
       <c r="B59" t="n">
-        <v>84228</v>
+        <v>91881</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7056,30 +7029,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3518</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7095,10 +7068,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753350</v>
+        <v>753390</v>
       </c>
       <c r="R59" t="n">
-        <v>7092106</v>
+        <v>7092305</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7158,10 +7131,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120403821</v>
+        <v>120403837</v>
       </c>
       <c r="B60" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7170,25 +7143,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7198,10 +7171,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753366</v>
+        <v>753040</v>
       </c>
       <c r="R60" t="n">
-        <v>7092147</v>
+        <v>7092152</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7260,7 +7233,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120403804</v>
+        <v>120403799</v>
       </c>
       <c r="B61" t="n">
         <v>91902</v>
@@ -7293,17 +7266,28 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>753034</v>
+        <v>752998</v>
       </c>
       <c r="R61" t="n">
-        <v>7092157</v>
+        <v>7092239</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7344,6 +7328,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7464,10 +7449,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120403834</v>
+        <v>120403816</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>84228</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7480,34 +7465,45 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>3518</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753316</v>
+        <v>753020</v>
       </c>
       <c r="R63" t="n">
-        <v>7092090</v>
+        <v>7092255</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7548,6 +7544,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7566,10 +7563,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120403817</v>
+        <v>120403812</v>
       </c>
       <c r="B64" t="n">
-        <v>84228</v>
+        <v>91862</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7578,37 +7575,29 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3518</v>
+        <v>4365</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
@@ -7617,10 +7606,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>752970</v>
+        <v>753389</v>
       </c>
       <c r="R64" t="n">
-        <v>7092203</v>
+        <v>7092245</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7653,6 +7642,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Under talllåga silverlåga</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7680,10 +7674,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120403797</v>
+        <v>120403820</v>
       </c>
       <c r="B65" t="n">
-        <v>91901</v>
+        <v>91850</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7696,21 +7690,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7720,10 +7714,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753023</v>
+        <v>753365</v>
       </c>
       <c r="R65" t="n">
-        <v>7092253</v>
+        <v>7092116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7756,11 +7750,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>stigen</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7787,10 +7776,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120403789</v>
+        <v>120403807</v>
       </c>
       <c r="B66" t="n">
-        <v>89292</v>
+        <v>57336</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7799,38 +7788,46 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6286</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>752993</v>
+        <v>753398</v>
       </c>
       <c r="R66" t="n">
-        <v>7092290</v>
+        <v>7092267</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7865,6 +7862,11 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>tall levande</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7873,6 +7875,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>Levande tall</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande tall</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7889,10 +7911,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120403800</v>
+        <v>120403808</v>
       </c>
       <c r="B67" t="n">
-        <v>91902</v>
+        <v>57336</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7905,34 +7927,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753420</v>
+        <v>753394</v>
       </c>
       <c r="R67" t="n">
-        <v>7092298</v>
+        <v>7092328</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7991,10 +8021,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120403813</v>
+        <v>120403814</v>
       </c>
       <c r="B68" t="n">
-        <v>91862</v>
+        <v>84228</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8003,30 +8033,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4365</v>
+        <v>3518</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8042,10 +8072,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753019</v>
+        <v>753350</v>
       </c>
       <c r="R68" t="n">
-        <v>7092243</v>
+        <v>7092106</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8078,11 +8108,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Mycel och fruktkroppar under hela tallågan</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8110,7 +8135,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120403836</v>
+        <v>120403834</v>
       </c>
       <c r="B69" t="n">
         <v>91858</v>
@@ -8150,10 +8175,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>753034</v>
+        <v>753316</v>
       </c>
       <c r="R69" t="n">
-        <v>7092157</v>
+        <v>7092090</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8212,10 +8237,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120403791</v>
+        <v>120403804</v>
       </c>
       <c r="B70" t="n">
-        <v>57473</v>
+        <v>91902</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8228,46 +8253,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>752978</v>
+        <v>753034</v>
       </c>
       <c r="R70" t="n">
-        <v>7092273</v>
+        <v>7092157</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8326,10 +8339,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120403794</v>
+        <v>120403821</v>
       </c>
       <c r="B71" t="n">
-        <v>91844</v>
+        <v>91850</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8342,41 +8355,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753399</v>
+        <v>753366</v>
       </c>
       <c r="R71" t="n">
-        <v>7092333</v>
+        <v>7092147</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8411,18 +8417,12 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -6460,10 +6460,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120403789</v>
+        <v>120403811</v>
       </c>
       <c r="B54" t="n">
-        <v>89292</v>
+        <v>91862</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6476,21 +6476,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6286</v>
+        <v>4365</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>752993</v>
+        <v>753330</v>
       </c>
       <c r="R54" t="n">
-        <v>7092290</v>
+        <v>7092111</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6536,6 +6536,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Under talllåga avbarkad</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6562,10 +6567,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120403811</v>
+        <v>120403794</v>
       </c>
       <c r="B55" t="n">
-        <v>91862</v>
+        <v>91844</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6574,38 +6579,45 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753330</v>
+        <v>753399</v>
       </c>
       <c r="R55" t="n">
-        <v>7092111</v>
+        <v>7092333</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6642,7 +6654,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Under talllåga avbarkad</t>
+          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6651,6 +6663,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6669,10 +6682,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120403794</v>
+        <v>120403789</v>
       </c>
       <c r="B56" t="n">
-        <v>91844</v>
+        <v>89292</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6681,45 +6694,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3100</v>
+        <v>6286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753399</v>
+        <v>752993</v>
       </c>
       <c r="R56" t="n">
-        <v>7092333</v>
+        <v>7092290</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6754,18 +6760,12 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6915,10 +6915,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120403835</v>
+        <v>120403826</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6927,38 +6927,49 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>752971</v>
+        <v>753390</v>
       </c>
       <c r="R58" t="n">
-        <v>7092254</v>
+        <v>7092305</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6999,6 +7010,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7017,10 +7029,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120403826</v>
+        <v>120403837</v>
       </c>
       <c r="B59" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7029,49 +7041,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753390</v>
+        <v>753040</v>
       </c>
       <c r="R59" t="n">
-        <v>7092305</v>
+        <v>7092152</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7112,7 +7113,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7131,7 +7131,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120403837</v>
+        <v>120403835</v>
       </c>
       <c r="B60" t="n">
         <v>91858</v>
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753040</v>
+        <v>752971</v>
       </c>
       <c r="R60" t="n">
-        <v>7092152</v>
+        <v>7092254</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7674,10 +7674,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120403820</v>
+        <v>120403807</v>
       </c>
       <c r="B65" t="n">
-        <v>91850</v>
+        <v>57336</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7690,34 +7690,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753365</v>
+        <v>753398</v>
       </c>
       <c r="R65" t="n">
-        <v>7092116</v>
+        <v>7092267</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7752,6 +7760,11 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>tall levande</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7760,6 +7773,26 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>Levande tall</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande tall</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7776,7 +7809,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120403807</v>
+        <v>120403808</v>
       </c>
       <c r="B66" t="n">
         <v>57336</v>
@@ -7824,10 +7857,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753398</v>
+        <v>753394</v>
       </c>
       <c r="R66" t="n">
-        <v>7092267</v>
+        <v>7092328</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7862,11 +7895,6 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>tall levande</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7875,26 +7903,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL66" t="inlineStr">
-        <is>
-          <t>Levande tall</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande tall</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7911,10 +7919,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120403808</v>
+        <v>120403820</v>
       </c>
       <c r="B67" t="n">
-        <v>57336</v>
+        <v>91850</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7927,42 +7935,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753394</v>
+        <v>753365</v>
       </c>
       <c r="R67" t="n">
-        <v>7092328</v>
+        <v>7092116</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -2622,7 +2622,7 @@
         <v>119799792</v>
       </c>
       <c r="B19" t="n">
-        <v>91904</v>
+        <v>92297</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>232140</v>
+        <v>5448</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ska återbesökas och dokumenteras ordentligt.</t>
+          <t>Ska återbesökas och dokumenteras ordentligt. Efter diskussion med validerare och experter: Troligen svartvit taggsvamp eller obeskriven art under arbetsnamn "mukkas skinn".</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8551,6 +8551,416 @@
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128785523</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>753406</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7092389</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128785500</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91486</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>753568</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7092277</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Funnen på mark nedanför tall, bilder</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128785496</v>
+      </c>
+      <c r="B75" t="n">
+        <v>90290</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>753583</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7092216</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128785516</v>
+      </c>
+      <c r="B76" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>753574</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7092215</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Vid stig</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -8556,7 +8556,7 @@
         <v>128785523</v>
       </c>
       <c r="B73" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>128785500</v>
       </c>
       <c r="B74" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128785516</v>
       </c>
       <c r="B76" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -8556,7 +8556,7 @@
         <v>128785523</v>
       </c>
       <c r="B73" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>128785500</v>
       </c>
       <c r="B74" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>128785496</v>
       </c>
       <c r="B75" t="n">
-        <v>90290</v>
+        <v>90317</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128785516</v>
       </c>
       <c r="B76" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -8556,7 +8556,7 @@
         <v>128785523</v>
       </c>
       <c r="B73" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>128785500</v>
       </c>
       <c r="B74" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>128785496</v>
       </c>
       <c r="B75" t="n">
-        <v>90317</v>
+        <v>90322</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128785516</v>
       </c>
       <c r="B76" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -8556,7 +8556,7 @@
         <v>128785523</v>
       </c>
       <c r="B73" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>128785500</v>
       </c>
       <c r="B74" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>128785496</v>
       </c>
       <c r="B75" t="n">
-        <v>90322</v>
+        <v>90327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128785516</v>
       </c>
       <c r="B76" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -8556,7 +8556,7 @@
         <v>128785523</v>
       </c>
       <c r="B73" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>128785500</v>
       </c>
       <c r="B74" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>128785496</v>
       </c>
       <c r="B75" t="n">
-        <v>90327</v>
+        <v>90331</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128785516</v>
       </c>
       <c r="B76" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -8556,7 +8556,7 @@
         <v>128785523</v>
       </c>
       <c r="B73" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>128785500</v>
       </c>
       <c r="B74" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>128785496</v>
       </c>
       <c r="B75" t="n">
-        <v>90331</v>
+        <v>90336</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128785516</v>
       </c>
       <c r="B76" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -8556,7 +8556,7 @@
         <v>128785523</v>
       </c>
       <c r="B73" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>128785500</v>
       </c>
       <c r="B74" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>128785496</v>
       </c>
       <c r="B75" t="n">
-        <v>90343</v>
+        <v>90346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128785516</v>
       </c>
       <c r="B76" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -8556,7 +8556,7 @@
         <v>128785523</v>
       </c>
       <c r="B73" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>128785500</v>
       </c>
       <c r="B74" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>128785496</v>
       </c>
       <c r="B75" t="n">
-        <v>90346</v>
+        <v>90349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128785516</v>
       </c>
       <c r="B76" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8961,6 +8961,107 @@
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129224532</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92857</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>752940</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7092218</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -8556,7 +8556,7 @@
         <v>128785523</v>
       </c>
       <c r="B73" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>128785500</v>
       </c>
       <c r="B74" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>128785496</v>
       </c>
       <c r="B75" t="n">
-        <v>90349</v>
+        <v>90353</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128785516</v>
       </c>
       <c r="B76" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>129224532</v>
       </c>
       <c r="B77" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -8556,7 +8556,7 @@
         <v>128785523</v>
       </c>
       <c r="B73" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>128785500</v>
       </c>
       <c r="B74" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>128785496</v>
       </c>
       <c r="B75" t="n">
-        <v>90353</v>
+        <v>90360</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128785516</v>
       </c>
       <c r="B76" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>129224532</v>
       </c>
       <c r="B77" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -8556,7 +8556,7 @@
         <v>128785523</v>
       </c>
       <c r="B73" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>128785500</v>
       </c>
       <c r="B74" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>128785496</v>
       </c>
       <c r="B75" t="n">
-        <v>90360</v>
+        <v>90362</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128785516</v>
       </c>
       <c r="B76" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>129224532</v>
       </c>
       <c r="B77" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -8556,7 +8556,7 @@
         <v>128785523</v>
       </c>
       <c r="B73" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>128785500</v>
       </c>
       <c r="B74" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>128785496</v>
       </c>
       <c r="B75" t="n">
-        <v>90362</v>
+        <v>90363</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>128785516</v>
       </c>
       <c r="B76" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>129224532</v>
       </c>
       <c r="B77" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -8966,7 +8966,7 @@
         <v>129224532</v>
       </c>
       <c r="B77" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -8966,7 +8966,7 @@
         <v>129224532</v>
       </c>
       <c r="B77" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54818449</v>
+        <v>79846257</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kullaheden, Klockarbäckens köpcentrum, Norra Kullavägen, Umedalen, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752957.7998153558</v>
+        <v>752974</v>
       </c>
       <c r="R2" t="n">
-        <v>7092183.518115247</v>
+        <v>7092142</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,71 +766,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>äldre sandtallskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Andreas Press</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Andreas Press</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54818448</v>
+        <v>103379714</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1593</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752955.6508063087</v>
+        <v>753108</v>
       </c>
       <c r="R3" t="n">
-        <v>7092204.594525988</v>
+        <v>7092218</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,38 +864,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>äldre sandtallskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54818450</v>
+        <v>103379717</v>
       </c>
       <c r="B4" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +894,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6276</v>
+        <v>1593</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753170.6051315637</v>
+        <v>753094</v>
       </c>
       <c r="R4" t="n">
-        <v>7092221.555515554</v>
+        <v>7092199</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +951,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,86 +965,70 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>äldre sandtallskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79846196</v>
+        <v>103379719</v>
       </c>
       <c r="B5" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>1593</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kullaheden, Klockarbäckens köpcentrum, Norra Kullavägen, Umedalen, Umeå, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752990.408600977</v>
+        <v>753063</v>
       </c>
       <c r="R5" t="n">
-        <v>7092164.021381939</v>
+        <v>7092160</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,22 +1052,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-09-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-09-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,33 +1066,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Press</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Press</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79846257</v>
+        <v>119797587</v>
       </c>
       <c r="B6" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,21 +1096,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>149</v>
+        <v>1593</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1186,25 +1118,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kullaheden, Klockarbäckens köpcentrum, Norra Kullavägen, Umedalen, Umeå, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752974.0247342621</v>
+        <v>752980</v>
       </c>
       <c r="R6" t="n">
-        <v>7092141.887408881</v>
+        <v>7092137</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,22 +1154,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-09-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-09-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Vid stigen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,66 +1179,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Andreas Press</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Andreas Press</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100665621</v>
+        <v>103379722</v>
       </c>
       <c r="B7" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753041.4309717159</v>
+        <v>753024</v>
       </c>
       <c r="R7" t="n">
-        <v>7092141.58817518</v>
+        <v>7092262</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,22 +1256,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,65 +1276,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103379719</v>
+        <v>103379723</v>
       </c>
       <c r="B8" t="n">
-        <v>87979</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1593</v>
+        <v>3100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753062.979453102</v>
+        <v>753029</v>
       </c>
       <c r="R8" t="n">
-        <v>7092160.156221122</v>
+        <v>7092253</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,28 +1356,17 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1499,15 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103379716</v>
+        <v>120403794</v>
       </c>
       <c r="B9" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1515,34 +1396,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753098.6955496365</v>
+        <v>753399</v>
       </c>
       <c r="R9" t="n">
-        <v>7092195.366731177</v>
+        <v>7092333</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,57 +1457,48 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103379706</v>
+        <v>119934744</v>
       </c>
       <c r="B10" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,34 +1506,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4745</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753018.1863918416</v>
+        <v>752933</v>
       </c>
       <c r="R10" t="n">
-        <v>7092149.446407621</v>
+        <v>7092206</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,22 +1563,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,33 +1577,49 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Tunn tallåga</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tunn tallåga</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103379709</v>
+        <v>120403787</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,34 +1627,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753114.3298525774</v>
+        <v>752945</v>
       </c>
       <c r="R11" t="n">
-        <v>7092166.527740129</v>
+        <v>7092283</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,22 +1684,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>nedfallen tallgren</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,68 +1703,95 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Nedfallen tallgren</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103379707</v>
+        <v>120403814</v>
       </c>
       <c r="B12" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>3518</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753004.6139237038</v>
+        <v>753350</v>
       </c>
       <c r="R12" t="n">
-        <v>7092136.394231946</v>
+        <v>7092106</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,22 +1818,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,55 +1832,51 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103379718</v>
+        <v>120403815</v>
       </c>
       <c r="B13" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>3518</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1987,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753062.979453102</v>
+        <v>752963</v>
       </c>
       <c r="R13" t="n">
-        <v>7092160.156221122</v>
+        <v>7092287</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,22 +1916,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,27 +1936,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103379704</v>
+        <v>120403816</v>
       </c>
       <c r="B14" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,34 +1959,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>3518</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>752990.6790377875</v>
+        <v>753020</v>
       </c>
       <c r="R14" t="n">
-        <v>7092199.017978681</v>
+        <v>7092255</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,22 +2024,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,68 +2038,75 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103379720</v>
+        <v>120403817</v>
       </c>
       <c r="B15" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6276</v>
+        <v>3518</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753042.883413361</v>
+        <v>752970</v>
       </c>
       <c r="R15" t="n">
-        <v>7092194.832277583</v>
+        <v>7092203</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,22 +2133,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,33 +2147,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103379724</v>
+        <v>103379711</v>
       </c>
       <c r="B16" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,21 +2177,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2323,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753012.7056677295</v>
+        <v>753179</v>
       </c>
       <c r="R16" t="n">
-        <v>7092277.389810262</v>
+        <v>7092238</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,19 +2234,9 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,15 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103379708</v>
+        <v>103379712</v>
       </c>
       <c r="B17" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,21 +2274,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2435,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753081.3213570006</v>
+        <v>753138</v>
       </c>
       <c r="R17" t="n">
-        <v>7092158.099504266</v>
+        <v>7092238</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,19 +2331,9 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,37 +2360,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103379703</v>
+        <v>103379716</v>
       </c>
       <c r="B18" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2547,10 +2395,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>752959.5341942665</v>
+        <v>753099</v>
       </c>
       <c r="R18" t="n">
-        <v>7092216.862060621</v>
+        <v>7092196</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2580,19 +2428,9 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2619,15 +2457,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119799792</v>
+        <v>103379718</v>
       </c>
       <c r="B19" t="n">
-        <v>92319</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2635,37 +2468,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>752934</v>
+        <v>753063</v>
       </c>
       <c r="R19" t="n">
-        <v>7092206</v>
+        <v>7092160</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,95 +2522,80 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ska återbesökas och dokumenteras ordentligt. Efter diskussion med validerare och experter: Troligen svartvit taggsvamp eller obeskriven art under arbetsnamn "mukkas skinn".</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119797587</v>
+        <v>120376699</v>
       </c>
       <c r="B20" t="n">
-        <v>89229</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1593</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752980</v>
+        <v>753325</v>
       </c>
       <c r="R20" t="n">
-        <v>7092137</v>
+        <v>7092121</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2804,17 +2619,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Vid stigen</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,49 +2649,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119797531</v>
+        <v>120403820</v>
       </c>
       <c r="B21" t="n">
-        <v>89292</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2881,10 +2696,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752941</v>
+        <v>753365</v>
       </c>
       <c r="R21" t="n">
-        <v>7092217</v>
+        <v>7092116</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2911,19 +2726,19 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
@@ -2943,15 +2758,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119797559</v>
+        <v>120403821</v>
       </c>
       <c r="B22" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2959,21 +2769,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2983,10 +2793,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752988</v>
+        <v>753366</v>
       </c>
       <c r="R22" t="n">
-        <v>7092133</v>
+        <v>7092147</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3013,12 +2823,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,37 +2855,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119808291</v>
+        <v>120403822</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3085,13 +2890,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753000</v>
+        <v>753418</v>
       </c>
       <c r="R23" t="n">
-        <v>7092192</v>
+        <v>7092398</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3115,22 +2920,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3145,27 +2940,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934744</v>
+        <v>120403823</v>
       </c>
       <c r="B24" t="n">
-        <v>90506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3173,37 +2963,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3242</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>752933</v>
+        <v>753408</v>
       </c>
       <c r="R24" t="n">
-        <v>7092206</v>
+        <v>7092342</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,12 +3017,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3244,29 +3031,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Tunn tallåga</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tunn tallåga</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3283,53 +3049,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120378409</v>
+        <v>54818449</v>
       </c>
       <c r="B25" t="n">
-        <v>89348</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753395</v>
+        <v>752958</v>
       </c>
       <c r="R25" t="n">
-        <v>7092342</v>
+        <v>7092184</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3353,22 +3114,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:48</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:48</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3379,31 +3130,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>äldre sandtallskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120378504</v>
+        <v>79846196</v>
       </c>
       <c r="B26" t="n">
-        <v>91939</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3411,37 +3162,47 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kullaheden, Klockarbäckens köpcentrum, Norra Kullavägen, Umedalen, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753400</v>
+        <v>752990</v>
       </c>
       <c r="R26" t="n">
-        <v>7092365</v>
+        <v>7092164</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3465,22 +3226,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2019-09-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2019-09-10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,27 +3246,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Andreas Press</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Andreas Press</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120374585</v>
+        <v>103379708</v>
       </c>
       <c r="B27" t="n">
-        <v>91941</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,37 +3269,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>752969</v>
+        <v>753081</v>
       </c>
       <c r="R27" t="n">
-        <v>7092237</v>
+        <v>7092158</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3577,22 +3323,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3607,27 +3343,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120374071</v>
+        <v>103379721</v>
       </c>
       <c r="B28" t="n">
-        <v>57488</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3635,37 +3366,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>752960</v>
+        <v>753035</v>
       </c>
       <c r="R28" t="n">
-        <v>7092251</v>
+        <v>7092249</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3689,22 +3420,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3719,65 +3440,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120374050</v>
+        <v>103379725</v>
       </c>
       <c r="B29" t="n">
-        <v>91913</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>752955</v>
+        <v>753014</v>
       </c>
       <c r="R29" t="n">
-        <v>7092262</v>
+        <v>7092299</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3801,22 +3517,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,27 +3537,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120376699</v>
+        <v>120403840</v>
       </c>
       <c r="B30" t="n">
-        <v>91905</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3859,37 +3560,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753325</v>
+        <v>753005</v>
       </c>
       <c r="R30" t="n">
-        <v>7092121</v>
+        <v>7092225</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3916,19 +3617,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,65 +3634,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120376488</v>
+        <v>54818448</v>
       </c>
       <c r="B31" t="n">
-        <v>89348</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753131</v>
+        <v>752956</v>
       </c>
       <c r="R31" t="n">
-        <v>7092136</v>
+        <v>7092205</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4025,22 +3711,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4051,31 +3727,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>äldre sandtallskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120374488</v>
+        <v>103379704</v>
       </c>
       <c r="B32" t="n">
-        <v>91941</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4083,37 +3759,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>752953</v>
+        <v>752991</v>
       </c>
       <c r="R32" t="n">
-        <v>7092257</v>
+        <v>7092199</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4137,22 +3813,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:56</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:56</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4167,27 +3833,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120378569</v>
+        <v>119718985</v>
       </c>
       <c r="B33" t="n">
-        <v>57488</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4195,37 +3856,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753416</v>
+        <v>752967</v>
       </c>
       <c r="R33" t="n">
-        <v>7092375</v>
+        <v>7092339</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4249,22 +3910,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4279,27 +3930,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120374037</v>
+        <v>119797605</v>
       </c>
       <c r="B34" t="n">
-        <v>91941</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4307,37 +3953,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753017</v>
+        <v>752888</v>
       </c>
       <c r="R34" t="n">
-        <v>7092260</v>
+        <v>7092191</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4361,22 +4007,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:27</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>09:27</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,27 +4027,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120375984</v>
+        <v>119808291</v>
       </c>
       <c r="B35" t="n">
-        <v>91941</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4419,37 +4050,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753131</v>
+        <v>753000</v>
       </c>
       <c r="R35" t="n">
-        <v>7092136</v>
+        <v>7092192</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4473,22 +4104,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4503,49 +4134,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120403789</v>
+        <v>119808299</v>
       </c>
       <c r="B36" t="n">
-        <v>89354</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4555,13 +4181,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>752993</v>
+        <v>752962</v>
       </c>
       <c r="R36" t="n">
-        <v>7092290</v>
+        <v>7092343</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4585,12 +4211,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4605,27 +4241,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120403800</v>
+        <v>120374050</v>
       </c>
       <c r="B37" t="n">
-        <v>91947</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4633,37 +4264,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753420</v>
+        <v>752955</v>
       </c>
       <c r="R37" t="n">
-        <v>7092298</v>
+        <v>7092262</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4690,9 +4321,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4707,31 +4348,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120403836</v>
+        <v>120403832</v>
       </c>
       <c r="B38" t="n">
-        <v>91919</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4759,10 +4395,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753034</v>
+        <v>753185</v>
       </c>
       <c r="R38" t="n">
-        <v>7092157</v>
+        <v>7092072</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4821,15 +4457,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120403824</v>
+        <v>120403833</v>
       </c>
       <c r="B39" t="n">
-        <v>91954</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4837,45 +4468,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753398</v>
+        <v>753327</v>
       </c>
       <c r="R39" t="n">
-        <v>7092356</v>
+        <v>7092129</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4916,7 +4536,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4935,15 +4554,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120403808</v>
+        <v>120403834</v>
       </c>
       <c r="B40" t="n">
-        <v>57351</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4951,42 +4565,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753394</v>
+        <v>753316</v>
       </c>
       <c r="R40" t="n">
-        <v>7092328</v>
+        <v>7092090</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5045,19 +4651,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120403837</v>
+        <v>120403835</v>
       </c>
       <c r="B41" t="n">
-        <v>91919</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5085,10 +4686,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753040</v>
+        <v>752971</v>
       </c>
       <c r="R41" t="n">
-        <v>7092152</v>
+        <v>7092254</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5147,15 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120403804</v>
+        <v>120403836</v>
       </c>
       <c r="B42" t="n">
-        <v>91947</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5163,21 +4759,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5249,15 +4845,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120403797</v>
+        <v>120403837</v>
       </c>
       <c r="B43" t="n">
-        <v>91945</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5265,21 +4856,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5289,10 +4880,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753023</v>
+        <v>753040</v>
       </c>
       <c r="R43" t="n">
-        <v>7092253</v>
+        <v>7092152</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5325,11 +4916,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>stigen</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5356,37 +4942,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120403835</v>
+        <v>120403811</v>
       </c>
       <c r="B44" t="n">
-        <v>91919</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5396,10 +4977,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>752971</v>
+        <v>753330</v>
       </c>
       <c r="R44" t="n">
-        <v>7092254</v>
+        <v>7092111</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5432,6 +5013,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Under talllåga avbarkad</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5458,49 +5044,36 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120403814</v>
+        <v>120403812</v>
       </c>
       <c r="B45" t="n">
-        <v>84257</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3518</v>
+        <v>4365</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -5509,10 +5082,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753350</v>
+        <v>753389</v>
       </c>
       <c r="R45" t="n">
-        <v>7092106</v>
+        <v>7092245</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5545,6 +5118,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Under talllåga silverlåga</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5572,50 +5150,56 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120403815</v>
+        <v>120403813</v>
       </c>
       <c r="B46" t="n">
-        <v>84257</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3518</v>
+        <v>4365</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>752963</v>
+        <v>753019</v>
       </c>
       <c r="R46" t="n">
-        <v>7092287</v>
+        <v>7092243</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5650,12 +5234,18 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Mycel och fruktkroppar under hela tallågan</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5674,15 +5264,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120403787</v>
+        <v>16580296</v>
       </c>
       <c r="B47" t="n">
-        <v>90570</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5690,37 +5275,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3242</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>752945</v>
+        <v>752967</v>
       </c>
       <c r="R47" t="n">
-        <v>7092283</v>
+        <v>7092346</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5747,17 +5329,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2014-09-10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>nedfallen tallgren</t>
+          <t>2014-09-10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5766,54 +5343,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Nedfallen tallgren</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Nedfallen tallgren</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120403823</v>
+        <v>103379703</v>
       </c>
       <c r="B48" t="n">
-        <v>91911</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5821,21 +5372,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5845,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>753408</v>
+        <v>752959</v>
       </c>
       <c r="R48" t="n">
-        <v>7092342</v>
+        <v>7092217</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5875,12 +5426,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5895,73 +5446,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120403813</v>
+        <v>103379706</v>
       </c>
       <c r="B49" t="n">
-        <v>91923</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4365</v>
+        <v>4745</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753019</v>
+        <v>753018</v>
       </c>
       <c r="R49" t="n">
-        <v>7092243</v>
+        <v>7092150</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5988,17 +5523,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Mycel och fruktkroppar under hela tallågan</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6007,34 +5537,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120403798</v>
+        <v>103379713</v>
       </c>
       <c r="B50" t="n">
-        <v>91947</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6042,21 +5566,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6066,10 +5590,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753328</v>
+        <v>753116</v>
       </c>
       <c r="R50" t="n">
-        <v>7092128</v>
+        <v>7092222</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6096,17 +5620,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>rikligt</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6121,27 +5640,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120403826</v>
+        <v>103379724</v>
       </c>
       <c r="B51" t="n">
-        <v>91954</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6149,45 +5663,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753390</v>
+        <v>753013</v>
       </c>
       <c r="R51" t="n">
-        <v>7092305</v>
+        <v>7092278</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6214,12 +5717,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6228,34 +5731,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120403821</v>
+        <v>103379727</v>
       </c>
       <c r="B52" t="n">
-        <v>91911</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6263,21 +5760,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6287,10 +5784,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>753366</v>
+        <v>753013</v>
       </c>
       <c r="R52" t="n">
-        <v>7092147</v>
+        <v>7092351</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6317,12 +5814,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6337,27 +5834,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120403792</v>
+        <v>54818447</v>
       </c>
       <c r="B53" t="n">
-        <v>90664</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6383,19 +5875,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>753398</v>
+        <v>752938</v>
       </c>
       <c r="R53" t="n">
-        <v>7092267</v>
+        <v>7092250</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6422,17 +5911,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Norrsidan lågt, gammal tall med spillkråkehack</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6441,84 +5925,71 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>äldre sandtallskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120403833</v>
+        <v>120403792</v>
       </c>
       <c r="B54" t="n">
-        <v>91919</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753327</v>
+        <v>753398</v>
       </c>
       <c r="R54" t="n">
-        <v>7092129</v>
+        <v>7092267</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6553,14 +6024,35 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Norrsidan lågt, gammal tall med spillkråkehack</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6577,15 +6069,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120403801</v>
+        <v>124428155</v>
       </c>
       <c r="B55" t="n">
-        <v>91947</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6593,34 +6080,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5449</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753319</v>
+        <v>753095</v>
       </c>
       <c r="R55" t="n">
-        <v>7092070</v>
+        <v>7092178</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6647,12 +6134,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6667,27 +6164,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Aron Dynesius</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Aron Dynesius</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120403820</v>
+        <v>128785500</v>
       </c>
       <c r="B56" t="n">
-        <v>91911</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6695,21 +6187,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6719,13 +6211,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753365</v>
+        <v>753568</v>
       </c>
       <c r="R56" t="n">
-        <v>7092116</v>
+        <v>7092277</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6749,12 +6241,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Funnen på mark nedanför tall, bilder</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6781,15 +6278,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120403817</v>
+        <v>120403788</v>
       </c>
       <c r="B57" t="n">
-        <v>84257</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6797,45 +6289,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3518</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>752970</v>
+        <v>753418</v>
       </c>
       <c r="R57" t="n">
-        <v>7092203</v>
+        <v>7092308</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6870,13 +6351,17 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>talllåga</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6895,15 +6380,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120403840</v>
+        <v>119799792</v>
       </c>
       <c r="B58" t="n">
-        <v>91913</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6911,34 +6391,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>753005</v>
+        <v>752934</v>
       </c>
       <c r="R58" t="n">
-        <v>7092225</v>
+        <v>7092206</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6965,20 +6448,26 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ska återbesökas och dokumenteras ordentligt. Efter diskussion med validerare och experter: Troligen svartvit taggsvamp eller obeskriven art under arbetsnamn "mukkas skinn".</t>
         </is>
       </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6997,56 +6486,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120403812</v>
+        <v>120378504</v>
       </c>
       <c r="B59" t="n">
-        <v>91923</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753389</v>
+        <v>753400</v>
       </c>
       <c r="R59" t="n">
-        <v>7092245</v>
+        <v>7092365</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7073,14 +6554,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Under talllåga silverlåga</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7089,56 +6575,50 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120403788</v>
+        <v>120403797</v>
       </c>
       <c r="B60" t="n">
-        <v>90609</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7148,10 +6628,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753418</v>
+        <v>753023</v>
       </c>
       <c r="R60" t="n">
-        <v>7092308</v>
+        <v>7092253</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7188,7 +6668,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>talllåga</t>
+          <t>stigen</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7215,15 +6695,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120403803</v>
+        <v>119797580</v>
       </c>
       <c r="B61" t="n">
-        <v>91947</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7231,21 +6706,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7255,10 +6730,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>752985</v>
+        <v>752975</v>
       </c>
       <c r="R61" t="n">
-        <v>7092284</v>
+        <v>7092134</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7285,12 +6760,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Vid stigen</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7317,61 +6797,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120403816</v>
+        <v>119797584</v>
       </c>
       <c r="B62" t="n">
-        <v>84257</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3518</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>753020</v>
+        <v>752960</v>
       </c>
       <c r="R62" t="n">
-        <v>7092255</v>
+        <v>7092140</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7398,12 +6862,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7412,7 +6876,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7431,37 +6894,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120403834</v>
+        <v>119797585</v>
       </c>
       <c r="B63" t="n">
-        <v>91919</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7471,10 +6929,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753316</v>
+        <v>753007</v>
       </c>
       <c r="R63" t="n">
-        <v>7092090</v>
+        <v>7092101</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7501,12 +6959,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7533,53 +6991,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120403790</v>
+        <v>120378684</v>
       </c>
       <c r="B64" t="n">
-        <v>89354</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6286</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753399</v>
+        <v>753401</v>
       </c>
       <c r="R64" t="n">
-        <v>7092350</v>
+        <v>7092390</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7606,9 +7059,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7623,27 +7086,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120403794</v>
+        <v>120403824</v>
       </c>
       <c r="B65" t="n">
-        <v>91944</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7651,29 +7109,33 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3100</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -7682,10 +7144,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753399</v>
+        <v>753398</v>
       </c>
       <c r="R65" t="n">
-        <v>7092333</v>
+        <v>7092356</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7720,16 +7182,11 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Kollekt insamlat för mikroskopering/DNA-analys</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
@@ -7750,50 +7207,56 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120403811</v>
+        <v>120403825</v>
       </c>
       <c r="B66" t="n">
-        <v>91923</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4365</v>
+        <v>5966</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753330</v>
+        <v>753142</v>
       </c>
       <c r="R66" t="n">
-        <v>7092111</v>
+        <v>7092136</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7830,7 +7293,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Under talllåga avbarkad</t>
+          <t>Invid stigen</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7839,6 +7302,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7857,15 +7321,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120403828</v>
+        <v>120403826</v>
       </c>
       <c r="B67" t="n">
-        <v>91954</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7890,17 +7349,28 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>752970</v>
+        <v>753390</v>
       </c>
       <c r="R67" t="n">
-        <v>7092257</v>
+        <v>7092305</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7941,6 +7411,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7959,15 +7430,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120403825</v>
+        <v>120403827</v>
       </c>
       <c r="B68" t="n">
-        <v>91954</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7992,28 +7458,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753142</v>
+        <v>753204</v>
       </c>
       <c r="R68" t="n">
-        <v>7092136</v>
+        <v>7092099</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8048,18 +7503,12 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Invid stigen</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8078,15 +7527,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120403791</v>
+        <v>120403828</v>
       </c>
       <c r="B69" t="n">
-        <v>57488</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8094,46 +7538,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>752978</v>
+        <v>752970</v>
       </c>
       <c r="R69" t="n">
-        <v>7092273</v>
+        <v>7092257</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8192,15 +7624,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120403799</v>
+        <v>128630175</v>
       </c>
       <c r="B70" t="n">
-        <v>91947</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8208,48 +7635,41 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>752998</v>
+        <v>752966</v>
       </c>
       <c r="R70" t="n">
-        <v>7092239</v>
+        <v>7092139</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8273,12 +7693,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8287,7 +7707,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8306,15 +7725,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120403807</v>
+        <v>128785514</v>
       </c>
       <c r="B71" t="n">
-        <v>57351</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8322,45 +7736,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753398</v>
+        <v>753595</v>
       </c>
       <c r="R71" t="n">
-        <v>7092267</v>
+        <v>7092460</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8384,17 +7790,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>tall levande</t>
+          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8405,26 +7811,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL71" t="inlineStr">
-        <is>
-          <t>Levande tall</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande tall</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8441,15 +7827,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124428155</v>
+        <v>128785516</v>
       </c>
       <c r="B72" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8457,37 +7838,41 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753095</v>
+        <v>753574</v>
       </c>
       <c r="R72" t="n">
-        <v>7092178</v>
+        <v>7092215</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8511,22 +7896,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8541,12 +7921,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Aron Dynesius</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Aron Dynesius</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8556,7 +7936,7 @@
         <v>128785523</v>
       </c>
       <c r="B73" t="n">
-        <v>92859</v>
+        <v>93235</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8654,10 +8034,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128785500</v>
+        <v>129224532</v>
       </c>
       <c r="B74" t="n">
-        <v>91560</v>
+        <v>93235</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8665,34 +8045,38 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>753568</v>
+        <v>752940</v>
       </c>
       <c r="R74" t="n">
-        <v>7092277</v>
+        <v>7092218</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8719,17 +8103,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Funnen på mark nedanför tall, bilder</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8756,10 +8135,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128785496</v>
+        <v>54818450</v>
       </c>
       <c r="B75" t="n">
-        <v>90363</v>
+        <v>90691</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8767,41 +8146,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753583</v>
+        <v>753171</v>
       </c>
       <c r="R75" t="n">
-        <v>7092216</v>
+        <v>7092222</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8825,84 +8200,85 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>äldre sandtallskog</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128785516</v>
+        <v>54818451</v>
       </c>
       <c r="B76" t="n">
-        <v>92859</v>
+        <v>90691</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>6276</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753574</v>
+        <v>753200</v>
       </c>
       <c r="R76" t="n">
-        <v>7092215</v>
+        <v>7092246</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8926,17 +8302,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Vid stig</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8947,68 +8318,69 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>äldre sandtallskog</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129224532</v>
+        <v>103379707</v>
       </c>
       <c r="B77" t="n">
-        <v>92901</v>
+        <v>90691</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5966</v>
+        <v>6276</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>752940</v>
+        <v>753004</v>
       </c>
       <c r="R77" t="n">
-        <v>7092218</v>
+        <v>7092136</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9032,12 +8404,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9052,15 +8424,2290 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>103379720</v>
+      </c>
+      <c r="B78" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>753043</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7092195</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2022-09-03</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2022-09-03</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>103379726</v>
+      </c>
+      <c r="B79" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>752993</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7092362</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2022-09-03</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2022-09-03</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>119797531</v>
+      </c>
+      <c r="B80" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>752941</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7092217</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
           <t>Roger Olofsson</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
+      <c r="AX80" t="inlineStr">
         <is>
           <t>Roger Olofsson</t>
         </is>
       </c>
-      <c r="AY77" t="inlineStr"/>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120376488</v>
+      </c>
+      <c r="B81" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>753131</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7092136</v>
+      </c>
+      <c r="S81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120377766</v>
+      </c>
+      <c r="B82" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>753373</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7092286</v>
+      </c>
+      <c r="S82" t="n">
+        <v>1</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120378409</v>
+      </c>
+      <c r="B83" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>753395</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7092342</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120403789</v>
+      </c>
+      <c r="B84" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>752993</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7092290</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120403790</v>
+      </c>
+      <c r="B85" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>753399</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7092350</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128627826</v>
+      </c>
+      <c r="B86" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>753005</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7092360</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128785496</v>
+      </c>
+      <c r="B87" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>753583</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7092216</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128785497</v>
+      </c>
+      <c r="B88" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>753408</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7092408</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>100665621</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79351</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>753041</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7092142</v>
+      </c>
+      <c r="S89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>J-M Roberge</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120403807</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>753398</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7092267</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>tall levande</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>Levande tall</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande tall</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120403808</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>753394</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7092328</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120403809</v>
+      </c>
+      <c r="B92" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>753402</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7092262</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>119797613</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57258</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>752974</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7092131</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Stannar upp och cirklar, tar höjd</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>120374071</v>
+      </c>
+      <c r="B94" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>752960</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7092251</v>
+      </c>
+      <c r="S94" t="n">
+        <v>1</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>120378569</v>
+      </c>
+      <c r="B95" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>753416</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7092375</v>
+      </c>
+      <c r="S95" t="n">
+        <v>1</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>120403791</v>
+      </c>
+      <c r="B96" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>752978</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7092273</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>119893175</v>
+      </c>
+      <c r="B97" t="n">
+        <v>93218</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>752982</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7092371</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>119893208</v>
+      </c>
+      <c r="B98" t="n">
+        <v>93218</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>752928</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7092309</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>119893225</v>
+      </c>
+      <c r="B99" t="n">
+        <v>93218</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>752927</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7092298</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AZ99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79846257</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379714</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379717</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379719</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797587</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379722</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379723</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403794</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934744</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,6 +1789,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403787</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403814</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1945,6 +2005,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403815</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2054,6 +2119,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403816</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2163,6 +2233,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403817</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2260,6 +2335,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379711</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2357,6 +2437,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379712</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2454,6 +2539,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379716</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2551,6 +2641,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379718</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2658,6 +2753,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120376699</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2755,6 +2855,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403820</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2852,6 +2957,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403821</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2949,6 +3059,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403822</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3046,6 +3161,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403823</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3148,6 +3268,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54818449</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3255,6 +3380,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79846196</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3352,6 +3482,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379708</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3449,6 +3584,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379721</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3546,6 +3686,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379725</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3643,6 +3788,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403840</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3745,6 +3895,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54818448</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3842,6 +3997,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379704</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3939,6 +4099,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718985</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4036,6 +4201,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797605</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4143,6 +4313,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808291</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4250,6 +4425,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808299</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4357,6 +4537,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120374050</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4454,6 +4639,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403832</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4551,6 +4741,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403833</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4648,6 +4843,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403834</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4745,6 +4945,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403835</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4842,6 +5047,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403836</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4939,6 +5149,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403837</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5041,6 +5256,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403811</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5147,6 +5367,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403812</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5261,6 +5486,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403813</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5358,6 +5588,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16580296</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5455,6 +5690,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379703</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5552,6 +5792,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379706</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5649,6 +5894,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379713</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5746,6 +5996,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379724</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5843,6 +6098,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379727</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5945,6 +6205,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54818447</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6066,6 +6331,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403792</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6173,6 +6443,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124428155</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6275,6 +6550,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785500</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6377,6 +6657,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403788</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6483,6 +6768,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119799792</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6590,6 +6880,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120378504</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6692,6 +6987,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403797</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6794,6 +7094,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797580</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6891,6 +7196,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797584</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6988,6 +7298,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797585</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7095,6 +7410,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120378684</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7204,6 +7524,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403824</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7318,6 +7643,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403825</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7427,6 +7757,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403826</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7524,6 +7859,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403827</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7621,6 +7961,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403828</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7722,6 +8067,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128630175</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7824,6 +8174,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785514</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7930,6 +8285,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785516</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8031,6 +8391,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785523</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8132,6 +8497,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224532</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8234,6 +8604,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54818450</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8336,6 +8711,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54818451</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8433,6 +8813,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379707</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8530,6 +8915,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379720</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8627,6 +9017,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379726</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8724,6 +9119,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797531</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8831,6 +9231,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120376488</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8938,6 +9343,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120377766</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9045,6 +9455,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120378409</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9142,6 +9557,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403789</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9239,6 +9659,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403790</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9336,6 +9761,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128627826</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9437,6 +9867,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785496</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9538,6 +9973,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785497</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9636,6 +10076,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100665621</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9766,6 +10211,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403807</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9871,6 +10321,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403808</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9976,6 +10431,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403809</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10100,6 +10560,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797613</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10207,6 +10672,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120374071</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10314,6 +10784,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120378569</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10423,6 +10898,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403791</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10518,6 +10998,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893175</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10613,6 +11098,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893208</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10708,8 +11198,113 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893225</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ99"/>
+  <dimension ref="A1:AZ100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5157,45 +5157,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120403811</v>
+        <v>136339094</v>
       </c>
       <c r="B44" t="n">
-        <v>93201</v>
+        <v>93378</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kullaskogen lilla sandgrop , Kullaskogen lilla sandgrop , Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753330</v>
+        <v>753004</v>
       </c>
       <c r="R44" t="n">
-        <v>7092111</v>
+        <v>7092301</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5222,17 +5231,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Under talllåga avbarkad</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5247,24 +5261,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403811</t>
+          <t>https://artportalen.se/Sighting/136339094</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120403812</v>
+        <v>120403811</v>
       </c>
       <c r="B45" t="n">
         <v>93201</v>
@@ -5293,19 +5307,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753389</v>
+        <v>753330</v>
       </c>
       <c r="R45" t="n">
-        <v>7092245</v>
+        <v>7092111</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5342,7 +5353,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Under talllåga silverlåga</t>
+          <t>Under talllåga avbarkad</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5351,7 +5362,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5369,13 +5379,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403812</t>
+          <t>https://artportalen.se/Sighting/120403811</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120403813</v>
+        <v>120403812</v>
       </c>
       <c r="B46" t="n">
         <v>93201</v>
@@ -5403,16 +5413,8 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -5421,10 +5423,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753019</v>
+        <v>753389</v>
       </c>
       <c r="R46" t="n">
-        <v>7092243</v>
+        <v>7092245</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5461,7 +5463,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Mycel och fruktkroppar under hela tallågan</t>
+          <t>Under talllåga silverlåga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5488,51 +5490,62 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403813</t>
+          <t>https://artportalen.se/Sighting/120403812</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16580296</v>
+        <v>120403813</v>
       </c>
       <c r="B47" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>752967</v>
+        <v>753019</v>
       </c>
       <c r="R47" t="n">
-        <v>7092346</v>
+        <v>7092243</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5559,12 +5572,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2014-09-10</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2014-09-10</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Mycel och fruktkroppar under hela tallågan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5573,30 +5591,31 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16580296</t>
+          <t>https://artportalen.se/Sighting/120403813</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>103379703</v>
+        <v>16580296</v>
       </c>
       <c r="B48" t="n">
         <v>93209</v>
@@ -5631,10 +5650,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>752959</v>
+        <v>752967</v>
       </c>
       <c r="R48" t="n">
-        <v>7092217</v>
+        <v>7092346</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5661,12 +5680,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2014-09-10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2014-09-10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5681,27 +5700,27 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379703</t>
+          <t>https://artportalen.se/Sighting/16580296</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>103379706</v>
+        <v>103379703</v>
       </c>
       <c r="B49" t="n">
-        <v>92841</v>
+        <v>93209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5709,21 +5728,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5733,10 +5752,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>753018</v>
+        <v>752959</v>
       </c>
       <c r="R49" t="n">
-        <v>7092150</v>
+        <v>7092217</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5794,13 +5813,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379706</t>
+          <t>https://artportalen.se/Sighting/103379703</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>103379713</v>
+        <v>103379706</v>
       </c>
       <c r="B50" t="n">
         <v>92841</v>
@@ -5835,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>753116</v>
+        <v>753018</v>
       </c>
       <c r="R50" t="n">
-        <v>7092222</v>
+        <v>7092150</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5896,13 +5915,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379713</t>
+          <t>https://artportalen.se/Sighting/103379706</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>103379724</v>
+        <v>103379713</v>
       </c>
       <c r="B51" t="n">
         <v>92841</v>
@@ -5937,10 +5956,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>753013</v>
+        <v>753116</v>
       </c>
       <c r="R51" t="n">
-        <v>7092278</v>
+        <v>7092222</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5998,13 +6017,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379724</t>
+          <t>https://artportalen.se/Sighting/103379713</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>103379727</v>
+        <v>103379724</v>
       </c>
       <c r="B52" t="n">
         <v>92841</v>
@@ -6042,7 +6061,7 @@
         <v>753013</v>
       </c>
       <c r="R52" t="n">
-        <v>7092351</v>
+        <v>7092278</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6100,16 +6119,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379727</t>
+          <t>https://artportalen.se/Sighting/103379724</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>54818447</v>
+        <v>103379727</v>
       </c>
       <c r="B53" t="n">
-        <v>91930</v>
+        <v>92841</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6117,21 +6136,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>4745</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6141,10 +6160,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>752938</v>
+        <v>753013</v>
       </c>
       <c r="R53" t="n">
-        <v>7092250</v>
+        <v>7092351</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6171,12 +6190,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6187,33 +6206,28 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>äldre sandtallskog</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54818447</t>
+          <t>https://artportalen.se/Sighting/103379727</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120403792</v>
+        <v>54818447</v>
       </c>
       <c r="B54" t="n">
         <v>91930</v>
@@ -6242,19 +6256,16 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>753398</v>
+        <v>752938</v>
       </c>
       <c r="R54" t="n">
-        <v>7092267</v>
+        <v>7092250</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6281,17 +6292,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Norrsidan lågt, gammal tall med spillkråkehack</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6300,46 +6306,35 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>äldre sandtallskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403792</t>
+          <t>https://artportalen.se/Sighting/54818447</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124428155</v>
+        <v>120403792</v>
       </c>
       <c r="B55" t="n">
         <v>91930</v>
@@ -6368,16 +6363,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>753095</v>
+        <v>753398</v>
       </c>
       <c r="R55" t="n">
-        <v>7092178</v>
+        <v>7092267</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6404,22 +6402,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:55</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Norrsidan lågt, gammal tall med spillkråkehack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6428,30 +6421,46 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Aron Dynesius</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Aron Dynesius</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124428155</t>
+          <t>https://artportalen.se/Sighting/120403792</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128785500</v>
+        <v>124428155</v>
       </c>
       <c r="B56" t="n">
         <v>91930</v>
@@ -6482,17 +6491,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>753568</v>
+        <v>753095</v>
       </c>
       <c r="R56" t="n">
-        <v>7092277</v>
+        <v>7092178</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6516,17 +6525,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Funnen på mark nedanför tall, bilder</t>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6541,49 +6555,49 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Aron Dynesius</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Aron Dynesius</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128785500</t>
+          <t>https://artportalen.se/Sighting/124428155</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120403788</v>
+        <v>128785500</v>
       </c>
       <c r="B57" t="n">
-        <v>91872</v>
+        <v>91930</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6593,13 +6607,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>753418</v>
+        <v>753568</v>
       </c>
       <c r="R57" t="n">
-        <v>7092308</v>
+        <v>7092277</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6623,17 +6637,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>talllåga</t>
+          <t>Funnen på mark nedanför tall, bilder</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6659,54 +6673,51 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403788</t>
+          <t>https://artportalen.se/Sighting/128785500</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119799792</v>
+        <v>120403788</v>
       </c>
       <c r="B58" t="n">
-        <v>93223</v>
+        <v>91872</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>752934</v>
+        <v>753418</v>
       </c>
       <c r="R58" t="n">
-        <v>7092206</v>
+        <v>7092308</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6733,26 +6744,25 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ska återbesökas och dokumenteras ordentligt. Efter diskussion med validerare och experter: Troligen svartvit taggsvamp eller obeskriven art under arbetsnamn "mukkas skinn".</t>
+          <t>talllåga</t>
         </is>
       </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF58" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6770,13 +6780,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119799792</t>
+          <t>https://artportalen.se/Sighting/120403788</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120378504</v>
+        <v>119799792</v>
       </c>
       <c r="B59" t="n">
         <v>93223</v>
@@ -6805,90 +6815,89 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>753400</v>
+        <v>752934</v>
       </c>
       <c r="R59" t="n">
-        <v>7092365</v>
+        <v>7092206</v>
       </c>
       <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ska återbesökas och dokumenteras ordentligt. Efter diskussion med validerare och experter: Troligen svartvit taggsvamp eller obeskriven art under arbetsnamn "mukkas skinn".</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
         <v>1</v>
       </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120378504</t>
+          <t>https://artportalen.se/Sighting/119799792</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120403797</v>
+        <v>120378504</v>
       </c>
       <c r="B60" t="n">
         <v>93223</v>
@@ -6919,17 +6928,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>753023</v>
+        <v>753400</v>
       </c>
       <c r="R60" t="n">
-        <v>7092253</v>
+        <v>7092365</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6956,14 +6965,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>stigen</t>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6978,27 +6992,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403797</t>
+          <t>https://artportalen.se/Sighting/120378504</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119797580</v>
+        <v>120403797</v>
       </c>
       <c r="B61" t="n">
-        <v>93235</v>
+        <v>93223</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7006,21 +7020,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7030,10 +7044,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>752975</v>
+        <v>753023</v>
       </c>
       <c r="R61" t="n">
-        <v>7092134</v>
+        <v>7092253</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7060,17 +7074,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Vid stigen</t>
+          <t>stigen</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7096,13 +7110,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797580</t>
+          <t>https://artportalen.se/Sighting/120403797</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119797584</v>
+        <v>119797580</v>
       </c>
       <c r="B62" t="n">
         <v>93235</v>
@@ -7137,10 +7151,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>752960</v>
+        <v>752975</v>
       </c>
       <c r="R62" t="n">
-        <v>7092140</v>
+        <v>7092134</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7175,6 +7189,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Vid stigen</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7198,13 +7217,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797584</t>
+          <t>https://artportalen.se/Sighting/119797580</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119797585</v>
+        <v>119797584</v>
       </c>
       <c r="B63" t="n">
         <v>93235</v>
@@ -7239,10 +7258,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>753007</v>
+        <v>752960</v>
       </c>
       <c r="R63" t="n">
-        <v>7092101</v>
+        <v>7092140</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7300,13 +7319,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797585</t>
+          <t>https://artportalen.se/Sighting/119797584</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120378684</v>
+        <v>119797585</v>
       </c>
       <c r="B64" t="n">
         <v>93235</v>
@@ -7337,17 +7356,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>753401</v>
+        <v>753007</v>
       </c>
       <c r="R64" t="n">
-        <v>7092390</v>
+        <v>7092101</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7371,22 +7390,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7401,24 +7410,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120378684</t>
+          <t>https://artportalen.se/Sighting/119797585</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120403824</v>
+        <v>120378684</v>
       </c>
       <c r="B65" t="n">
         <v>93235</v>
@@ -7446,31 +7455,20 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>753398</v>
+        <v>753401</v>
       </c>
       <c r="R65" t="n">
-        <v>7092356</v>
+        <v>7092390</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7497,42 +7495,51 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403824</t>
+          <t>https://artportalen.se/Sighting/120378684</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120403825</v>
+        <v>120403824</v>
       </c>
       <c r="B66" t="n">
         <v>93235</v>
@@ -7562,7 +7569,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7578,10 +7585,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>753142</v>
+        <v>753398</v>
       </c>
       <c r="R66" t="n">
-        <v>7092136</v>
+        <v>7092356</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7616,11 +7623,6 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Invid stigen</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7645,13 +7647,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403825</t>
+          <t>https://artportalen.se/Sighting/120403824</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120403826</v>
+        <v>120403825</v>
       </c>
       <c r="B67" t="n">
         <v>93235</v>
@@ -7681,7 +7683,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7697,10 +7699,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>753390</v>
+        <v>753142</v>
       </c>
       <c r="R67" t="n">
-        <v>7092305</v>
+        <v>7092136</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,6 +7737,11 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Invid stigen</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7759,13 +7766,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403826</t>
+          <t>https://artportalen.se/Sighting/120403825</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120403827</v>
+        <v>120403826</v>
       </c>
       <c r="B68" t="n">
         <v>93235</v>
@@ -7793,17 +7800,28 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>753204</v>
+        <v>753390</v>
       </c>
       <c r="R68" t="n">
-        <v>7092099</v>
+        <v>7092305</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7844,6 +7862,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7861,13 +7880,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403827</t>
+          <t>https://artportalen.se/Sighting/120403826</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120403828</v>
+        <v>120403827</v>
       </c>
       <c r="B69" t="n">
         <v>93235</v>
@@ -7902,10 +7921,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>752970</v>
+        <v>753204</v>
       </c>
       <c r="R69" t="n">
-        <v>7092257</v>
+        <v>7092099</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7963,13 +7982,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403828</t>
+          <t>https://artportalen.se/Sighting/120403827</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128630175</v>
+        <v>120403828</v>
       </c>
       <c r="B70" t="n">
         <v>93235</v>
@@ -7997,24 +8016,20 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>752966</v>
+        <v>752970</v>
       </c>
       <c r="R70" t="n">
-        <v>7092139</v>
+        <v>7092257</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8038,12 +8053,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8069,13 +8084,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128630175</t>
+          <t>https://artportalen.se/Sighting/120403828</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128785514</v>
+        <v>128630175</v>
       </c>
       <c r="B71" t="n">
         <v>93235</v>
@@ -8103,17 +8118,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>753595</v>
+        <v>752966</v>
       </c>
       <c r="R71" t="n">
-        <v>7092460</v>
+        <v>7092139</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8140,17 +8159,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Vid stig</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8176,13 +8190,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128785514</t>
+          <t>https://artportalen.se/Sighting/128630175</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128785516</v>
+        <v>128785514</v>
       </c>
       <c r="B72" t="n">
         <v>93235</v>
@@ -8210,21 +8224,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>753574</v>
+        <v>753595</v>
       </c>
       <c r="R72" t="n">
-        <v>7092215</v>
+        <v>7092460</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8287,13 +8297,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128785516</t>
+          <t>https://artportalen.se/Sighting/128785514</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128785523</v>
+        <v>128785516</v>
       </c>
       <c r="B73" t="n">
         <v>93235</v>
@@ -8323,7 +8333,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8332,10 +8342,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>753406</v>
+        <v>753574</v>
       </c>
       <c r="R73" t="n">
-        <v>7092389</v>
+        <v>7092215</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8362,12 +8372,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8393,13 +8408,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128785523</t>
+          <t>https://artportalen.se/Sighting/128785516</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129224532</v>
+        <v>128785523</v>
       </c>
       <c r="B74" t="n">
         <v>93235</v>
@@ -8429,7 +8444,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8438,10 +8453,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>752940</v>
+        <v>753406</v>
       </c>
       <c r="R74" t="n">
-        <v>7092218</v>
+        <v>7092389</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8468,12 +8483,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8499,54 +8514,58 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129224532</t>
+          <t>https://artportalen.se/Sighting/128785523</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>54818450</v>
+        <v>129224532</v>
       </c>
       <c r="B75" t="n">
-        <v>90691</v>
+        <v>93235</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>753171</v>
+        <v>752940</v>
       </c>
       <c r="R75" t="n">
-        <v>7092222</v>
+        <v>7092218</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8570,12 +8589,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8586,33 +8605,28 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>äldre sandtallskog</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54818450</t>
+          <t>https://artportalen.se/Sighting/129224532</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>54818451</v>
+        <v>54818450</v>
       </c>
       <c r="B76" t="n">
         <v>90691</v>
@@ -8647,10 +8661,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>753200</v>
+        <v>753171</v>
       </c>
       <c r="R76" t="n">
-        <v>7092246</v>
+        <v>7092222</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8713,13 +8727,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54818451</t>
+          <t>https://artportalen.se/Sighting/54818450</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>103379707</v>
+        <v>54818451</v>
       </c>
       <c r="B77" t="n">
         <v>90691</v>
@@ -8754,10 +8768,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>753004</v>
+        <v>753200</v>
       </c>
       <c r="R77" t="n">
-        <v>7092136</v>
+        <v>7092246</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8784,12 +8798,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8800,28 +8814,33 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>äldre sandtallskog</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379707</t>
+          <t>https://artportalen.se/Sighting/54818451</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>103379720</v>
+        <v>103379707</v>
       </c>
       <c r="B78" t="n">
         <v>90691</v>
@@ -8856,10 +8875,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>753043</v>
+        <v>753004</v>
       </c>
       <c r="R78" t="n">
-        <v>7092195</v>
+        <v>7092136</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8917,13 +8936,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379720</t>
+          <t>https://artportalen.se/Sighting/103379707</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>103379726</v>
+        <v>103379720</v>
       </c>
       <c r="B79" t="n">
         <v>90691</v>
@@ -8958,10 +8977,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>752993</v>
+        <v>753043</v>
       </c>
       <c r="R79" t="n">
-        <v>7092362</v>
+        <v>7092195</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9019,16 +9038,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379726</t>
+          <t>https://artportalen.se/Sighting/103379720</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119797531</v>
+        <v>103379726</v>
       </c>
       <c r="B80" t="n">
-        <v>90710</v>
+        <v>90691</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9036,21 +9055,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9060,10 +9079,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>752941</v>
+        <v>752993</v>
       </c>
       <c r="R80" t="n">
-        <v>7092217</v>
+        <v>7092362</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9090,19 +9109,19 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="b">
         <v>0</v>
@@ -9110,24 +9129,24 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797531</t>
+          <t>https://artportalen.se/Sighting/103379726</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120376488</v>
+        <v>119797531</v>
       </c>
       <c r="B81" t="n">
         <v>90710</v>
@@ -9158,63 +9177,53 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>753131</v>
+        <v>752941</v>
       </c>
       <c r="R81" t="n">
-        <v>7092136</v>
+        <v>7092217</v>
       </c>
       <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
         <v>1</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
       </c>
       <c r="AG81" t="b">
         <v>0</v>
@@ -9222,24 +9231,24 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120376488</t>
+          <t>https://artportalen.se/Sighting/119797531</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120377766</v>
+        <v>120376488</v>
       </c>
       <c r="B82" t="n">
         <v>90710</v>
@@ -9274,10 +9283,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>753373</v>
+        <v>753131</v>
       </c>
       <c r="R82" t="n">
-        <v>7092286</v>
+        <v>7092136</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9309,7 +9318,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9319,7 +9328,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9345,13 +9354,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120377766</t>
+          <t>https://artportalen.se/Sighting/120376488</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120378409</v>
+        <v>120377766</v>
       </c>
       <c r="B83" t="n">
         <v>90710</v>
@@ -9386,10 +9395,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>753395</v>
+        <v>753373</v>
       </c>
       <c r="R83" t="n">
-        <v>7092342</v>
+        <v>7092286</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9421,7 +9430,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9440,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9457,13 +9466,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120378409</t>
+          <t>https://artportalen.se/Sighting/120377766</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120403789</v>
+        <v>120378409</v>
       </c>
       <c r="B84" t="n">
         <v>90710</v>
@@ -9494,17 +9503,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>752993</v>
+        <v>753395</v>
       </c>
       <c r="R84" t="n">
-        <v>7092290</v>
+        <v>7092342</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9531,9 +9540,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9548,24 +9567,24 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403789</t>
+          <t>https://artportalen.se/Sighting/120378409</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120403790</v>
+        <v>120403789</v>
       </c>
       <c r="B85" t="n">
         <v>90710</v>
@@ -9600,10 +9619,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>753399</v>
+        <v>752993</v>
       </c>
       <c r="R85" t="n">
-        <v>7092350</v>
+        <v>7092290</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9661,13 +9680,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403790</t>
+          <t>https://artportalen.se/Sighting/120403789</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128627826</v>
+        <v>120403790</v>
       </c>
       <c r="B86" t="n">
         <v>90710</v>
@@ -9702,10 +9721,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>753005</v>
+        <v>753399</v>
       </c>
       <c r="R86" t="n">
-        <v>7092360</v>
+        <v>7092350</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9732,12 +9751,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9752,24 +9771,24 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128627826</t>
+          <t>https://artportalen.se/Sighting/120403790</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128785496</v>
+        <v>128627826</v>
       </c>
       <c r="B87" t="n">
         <v>90710</v>
@@ -9797,24 +9816,20 @@
           <t>(Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>753583</v>
+        <v>753005</v>
       </c>
       <c r="R87" t="n">
-        <v>7092216</v>
+        <v>7092360</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9838,19 +9853,19 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="b">
         <v>0</v>
@@ -9858,24 +9873,24 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128785496</t>
+          <t>https://artportalen.se/Sighting/128627826</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128785497</v>
+        <v>128785496</v>
       </c>
       <c r="B88" t="n">
         <v>90710</v>
@@ -9905,7 +9920,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9914,10 +9929,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>753408</v>
+        <v>753583</v>
       </c>
       <c r="R88" t="n">
-        <v>7092408</v>
+        <v>7092216</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9944,12 +9959,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9975,55 +9990,58 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128785497</t>
+          <t>https://artportalen.se/Sighting/128785496</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>100665621</v>
+        <v>128785497</v>
       </c>
       <c r="B89" t="n">
-        <v>79351</v>
+        <v>90710</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6434</v>
+        <v>6286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>753041</v>
+        <v>753408</v>
       </c>
       <c r="R89" t="n">
-        <v>7092142</v>
+        <v>7092408</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10047,19 +10065,19 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -10067,27 +10085,27 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100665621</t>
+          <t>https://artportalen.se/Sighting/128785497</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120403807</v>
+        <v>100665621</v>
       </c>
       <c r="B90" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10095,45 +10113,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>753398</v>
+        <v>753041</v>
       </c>
       <c r="R90" t="n">
-        <v>7092267</v>
+        <v>7092142</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10157,17 +10168,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2022-05-09</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>tall levande</t>
+          <t>2022-05-09</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10178,48 +10184,28 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL90" t="inlineStr">
-        <is>
-          <t>Levande tall</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande tall</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403807</t>
+          <t>https://artportalen.se/Sighting/100665621</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120403808</v>
+        <v>120403807</v>
       </c>
       <c r="B91" t="n">
         <v>57950</v>
@@ -10262,10 +10248,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>753394</v>
+        <v>753398</v>
       </c>
       <c r="R91" t="n">
-        <v>7092328</v>
+        <v>7092267</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10300,6 +10286,11 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>tall levande</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10308,6 +10299,26 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>Levande tall</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande tall</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -10323,13 +10334,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403808</t>
+          <t>https://artportalen.se/Sighting/120403807</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120403809</v>
+        <v>120403808</v>
       </c>
       <c r="B92" t="n">
         <v>57950</v>
@@ -10372,10 +10383,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753402</v>
+        <v>753394</v>
       </c>
       <c r="R92" t="n">
-        <v>7092262</v>
+        <v>7092328</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10433,16 +10444,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403809</t>
+          <t>https://artportalen.se/Sighting/120403808</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119797613</v>
+        <v>120403809</v>
       </c>
       <c r="B93" t="n">
-        <v>57258</v>
+        <v>57950</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10450,16 +10461,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -10467,16 +10478,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -10486,10 +10493,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>752974</v>
+        <v>753402</v>
       </c>
       <c r="R93" t="n">
-        <v>7092131</v>
+        <v>7092262</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10516,27 +10523,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Stannar upp och cirklar, tar höjd</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10562,54 +10554,66 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797613</t>
+          <t>https://artportalen.se/Sighting/120403809</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120374071</v>
+        <v>119797613</v>
       </c>
       <c r="B94" t="n">
-        <v>58114</v>
+        <v>57258</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>100065</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>752960</v>
+        <v>752974</v>
       </c>
       <c r="R94" t="n">
-        <v>7092251</v>
+        <v>7092131</v>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10633,22 +10637,27 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Stannar upp och cirklar, tar höjd</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10663,24 +10672,24 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120374071</t>
+          <t>https://artportalen.se/Sighting/119797613</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120378569</v>
+        <v>120374071</v>
       </c>
       <c r="B95" t="n">
         <v>58114</v>
@@ -10711,14 +10720,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>753416</v>
+        <v>752960</v>
       </c>
       <c r="R95" t="n">
-        <v>7092375</v>
+        <v>7092251</v>
       </c>
       <c r="S95" t="n">
         <v>1</v>
@@ -10750,7 +10759,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10760,7 +10769,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10786,13 +10795,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120378569</t>
+          <t>https://artportalen.se/Sighting/120374071</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120403791</v>
+        <v>120378569</v>
       </c>
       <c r="B96" t="n">
         <v>58114</v>
@@ -10820,32 +10829,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>752978</v>
+        <v>753416</v>
       </c>
       <c r="R96" t="n">
-        <v>7092273</v>
+        <v>7092375</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10872,9 +10869,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10889,27 +10896,27 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403791</t>
+          <t>https://artportalen.se/Sighting/120378569</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119893175</v>
+        <v>120403791</v>
       </c>
       <c r="B97" t="n">
-        <v>93218</v>
+        <v>58114</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10917,31 +10924,46 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6331648</v>
+        <v>103021</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellodon aquiloniniger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>A.M.Ainsw. &amp; Svantesson</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>752982</v>
+        <v>752978</v>
       </c>
       <c r="R97" t="n">
-        <v>7092371</v>
+        <v>7092273</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10968,12 +10990,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10982,31 +11004,30 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893175</t>
+          <t>https://artportalen.se/Sighting/120403791</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119893208</v>
+        <v>119893175</v>
       </c>
       <c r="B98" t="n">
         <v>93218</v>
@@ -11038,10 +11059,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>752928</v>
+        <v>752982</v>
       </c>
       <c r="R98" t="n">
-        <v>7092309</v>
+        <v>7092371</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11100,13 +11121,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893208</t>
+          <t>https://artportalen.se/Sighting/119893175</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119893225</v>
+        <v>119893208</v>
       </c>
       <c r="B99" t="n">
         <v>93218</v>
@@ -11138,10 +11159,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>752927</v>
+        <v>752928</v>
       </c>
       <c r="R99" t="n">
-        <v>7092298</v>
+        <v>7092309</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11199,6 +11220,106 @@
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893208</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>119893225</v>
+      </c>
+      <c r="B100" t="n">
+        <v>93218</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>752927</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7092298</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119893225</t>
         </is>
@@ -11304,6 +11425,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -5160,7 +5160,7 @@
         <v>136339094</v>
       </c>
       <c r="B44" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -5160,7 +5160,7 @@
         <v>136339094</v>
       </c>
       <c r="B44" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -5160,7 +5160,7 @@
         <v>136339094</v>
       </c>
       <c r="B44" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -5160,7 +5160,7 @@
         <v>136339094</v>
       </c>
       <c r="B44" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
